--- a/RR_Results/dm_results_fullset_iteratedpredictions_30-Oct-2024.xlsx
+++ b/RR_Results/dm_results_fullset_iteratedpredictions_30-Oct-2024.xlsx
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="1070" uniqueCount="503">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="1082" uniqueCount="507">
   <si>
     <t>Row</t>
   </si>
@@ -124,6 +124,9 @@
     <t>RMSFE_Covid</t>
   </si>
   <si>
+    <t>RMSFE_Pre</t>
+  </si>
+  <si>
     <t>RMSFE_Full</t>
   </si>
   <si>
@@ -136,6 +139,9 @@
     <t>CRPS_Covid</t>
   </si>
   <si>
+    <t>CRPS_Pre</t>
+  </si>
+  <si>
     <t>CRPS_Full</t>
   </si>
   <si>
@@ -157,6 +163,12 @@
     <t>DM_pv_joint_Covid</t>
   </si>
   <si>
+    <t>DM_joint_Pre</t>
+  </si>
+  <si>
+    <t>DM_pv_joint_Pre</t>
+  </si>
+  <si>
     <t>DM_joint_Full</t>
   </si>
   <si>
@@ -181,16 +193,16 @@
     <t>DM_CRPS_pv_joint_Covid</t>
   </si>
   <si>
+    <t>DM_CRPS_joint_Pre</t>
+  </si>
+  <si>
+    <t>DM_CRPS_pv_joint_Pre</t>
+  </si>
+  <si>
     <t>DM_CRPS_joint_Full</t>
   </si>
   <si>
     <t>DM_CRPS_pv_joint_Full</t>
-  </si>
-  <si>
-    <t>RMSFE_Pre</t>
-  </si>
-  <si>
-    <t>CRPS_Pre</t>
   </si>
   <si>
     <t>dmpv_pre_nowcast_ms1</t>
@@ -2804,61 +2816,61 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="I1" s="0" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="J1" s="0" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="K1" s="0" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="L1" s="0" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="M1" s="0" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="N1" s="0" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="O1" s="0" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="P1" s="0" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="Q1" s="0" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="R1" s="0" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="S1" s="0" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="T1" s="0" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
     </row>
     <row r="2">
@@ -4075,61 +4087,61 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="I1" s="0" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="J1" s="0" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="K1" s="0" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="L1" s="0" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="M1" s="0" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="N1" s="0" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="O1" s="0" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="P1" s="0" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="Q1" s="0" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="R1" s="0" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="S1" s="0" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="T1" s="0" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
     </row>
     <row r="2">
@@ -5346,61 +5358,61 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="I1" s="0" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="J1" s="0" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="K1" s="0" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="L1" s="0" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="M1" s="0" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="N1" s="0" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="O1" s="0" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="P1" s="0" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="Q1" s="0" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="R1" s="0" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="S1" s="0" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="T1" s="0" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
     </row>
     <row r="2">
@@ -6617,61 +6629,61 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="I1" s="0" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="J1" s="0" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="K1" s="0" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="L1" s="0" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="M1" s="0" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="N1" s="0" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="O1" s="0" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="P1" s="0" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="Q1" s="0" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="R1" s="0" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="S1" s="0" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="T1" s="0" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="2">
@@ -7888,61 +7900,61 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="I1" s="0" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="J1" s="0" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="K1" s="0" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="L1" s="0" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="M1" s="0" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="N1" s="0" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="O1" s="0" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="P1" s="0" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="Q1" s="0" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="R1" s="0" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="S1" s="0" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="T1" s="0" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
     </row>
     <row r="2">
@@ -9129,7 +9141,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Y21"/>
+  <dimension ref="A1:AE21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="22.85546875" customWidth="true"/>
@@ -9138,25 +9150,31 @@
     <col min="4" max="4" width="13" customWidth="true"/>
     <col min="5" max="5" width="12.7109375" customWidth="true"/>
     <col min="6" max="6" width="12.7109375" customWidth="true"/>
-    <col min="7" max="7" width="13.85546875" customWidth="true"/>
-    <col min="8" max="8" width="11.7109375" customWidth="true"/>
-    <col min="9" max="9" width="12.7109375" customWidth="true"/>
-    <col min="10" max="10" width="13.7109375" customWidth="true"/>
-    <col min="11" max="11" width="16.85546875" customWidth="true"/>
-    <col min="12" max="12" width="17.5703125" customWidth="true"/>
-    <col min="13" max="13" width="20.7109375" customWidth="true"/>
-    <col min="14" max="14" width="15.28515625" customWidth="true"/>
-    <col min="15" max="15" width="18.42578125" customWidth="true"/>
-    <col min="16" max="16" width="13.5703125" customWidth="true"/>
-    <col min="17" max="17" width="16.7109375" customWidth="true"/>
-    <col min="18" max="18" width="19.140625" customWidth="true"/>
-    <col min="19" max="19" width="22.28515625" customWidth="true"/>
-    <col min="20" max="20" width="23" customWidth="true"/>
-    <col min="21" max="21" width="26.140625" customWidth="true"/>
-    <col min="22" max="22" width="20.7109375" customWidth="true"/>
-    <col min="23" max="23" width="23.85546875" customWidth="true"/>
-    <col min="24" max="24" width="19" customWidth="true"/>
-    <col min="25" max="25" width="22.140625" customWidth="true"/>
+    <col min="7" max="7" width="12.7109375" customWidth="true"/>
+    <col min="8" max="8" width="13.85546875" customWidth="true"/>
+    <col min="9" max="9" width="11.7109375" customWidth="true"/>
+    <col min="10" max="10" width="12.7109375" customWidth="true"/>
+    <col min="11" max="11" width="12.7109375" customWidth="true"/>
+    <col min="12" max="12" width="13.7109375" customWidth="true"/>
+    <col min="13" max="13" width="16.85546875" customWidth="true"/>
+    <col min="14" max="14" width="17.5703125" customWidth="true"/>
+    <col min="15" max="15" width="20.7109375" customWidth="true"/>
+    <col min="16" max="16" width="15.28515625" customWidth="true"/>
+    <col min="17" max="17" width="18.42578125" customWidth="true"/>
+    <col min="18" max="18" width="13.42578125" customWidth="true"/>
+    <col min="19" max="19" width="16.42578125" customWidth="true"/>
+    <col min="20" max="20" width="13.5703125" customWidth="true"/>
+    <col min="21" max="21" width="16.7109375" customWidth="true"/>
+    <col min="22" max="22" width="19.140625" customWidth="true"/>
+    <col min="23" max="23" width="22.28515625" customWidth="true"/>
+    <col min="24" max="24" width="23" customWidth="true"/>
+    <col min="25" max="25" width="26.140625" customWidth="true"/>
+    <col min="26" max="26" width="20.7109375" customWidth="true"/>
+    <col min="27" max="27" width="23.85546875" customWidth="true"/>
+    <col min="28" max="28" width="18.7109375" customWidth="true"/>
+    <col min="29" max="29" width="21.85546875" customWidth="true"/>
+    <col min="30" max="30" width="19" customWidth="true"/>
+    <col min="31" max="31" width="22.140625" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9235,6 +9253,24 @@
       <c r="Y1" s="0" t="s">
         <v>44</v>
       </c>
+      <c r="Z1" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA1" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB1" s="0" t="s">
+        <v>47</v>
+      </c>
+      <c r="AC1" s="0" t="s">
+        <v>48</v>
+      </c>
+      <c r="AD1" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="AE1" s="0" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
@@ -9250,22 +9286,26 @@
         <v>4.6019600853021281</v>
       </c>
       <c r="E2" s="0">
+        <v>0.53720643100740673</v>
+      </c>
+      <c r="F2" s="0">
         <v>2.1680245344647679</v>
       </c>
-      <c r="F2" s="0">
+      <c r="G2" s="0">
         <v>0.62459268058674622</v>
       </c>
-      <c r="G2" s="0">
+      <c r="H2" s="0">
         <v>0.4251177849662891</v>
       </c>
-      <c r="H2" s="0">
+      <c r="I2" s="0">
         <v>2.6510521379640259</v>
       </c>
-      <c r="I2" s="0">
+      <c r="J2" s="0">
+        <v>0.47115045318639465</v>
+      </c>
+      <c r="K2" s="0">
         <v>0.90713079014192111</v>
       </c>
-      <c r="J2" s="0"/>
-      <c r="K2" s="0"/>
       <c r="L2" s="0"/>
       <c r="M2" s="0"/>
       <c r="N2" s="0"/>
@@ -9280,6 +9320,12 @@
       <c r="W2" s="0"/>
       <c r="X2" s="0"/>
       <c r="Y2" s="0"/>
+      <c r="Z2" s="0"/>
+      <c r="AA2" s="0"/>
+      <c r="AB2" s="0"/>
+      <c r="AC2" s="0"/>
+      <c r="AD2" s="0"/>
+      <c r="AE2" s="0"/>
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
@@ -9295,66 +9341,84 @@
         <v>1.257095935588681</v>
       </c>
       <c r="E3" s="0">
+        <v>0.91143797697262752</v>
+      </c>
+      <c r="F3" s="0">
         <v>1.1867838311219354</v>
       </c>
-      <c r="F3" s="0">
+      <c r="G3" s="0">
         <v>0.86846838861046061</v>
       </c>
-      <c r="G3" s="0">
+      <c r="H3" s="0">
         <v>0.58551396615861029</v>
       </c>
-      <c r="H3" s="0">
+      <c r="I3" s="0">
         <v>1.108954861607153</v>
       </c>
-      <c r="I3" s="0">
+      <c r="J3" s="0">
+        <v>0.67207683991769573</v>
+      </c>
+      <c r="K3" s="0">
         <v>0.92742842229494715</v>
       </c>
-      <c r="J3" s="0">
+      <c r="L3" s="0">
         <v>1.8408903383245745</v>
       </c>
-      <c r="K3" s="0">
+      <c r="M3" s="0">
         <v>0.066942719695817929</v>
       </c>
-      <c r="L3" s="0">
+      <c r="N3" s="0">
         <v>17.795868593157135</v>
       </c>
-      <c r="M3" s="0">
+      <c r="O3" s="0">
         <v>1.7859991724669844e-59</v>
       </c>
-      <c r="N3" s="0">
+      <c r="P3" s="0">
         <v>-2.8240376414260639</v>
       </c>
-      <c r="O3" s="0">
+      <c r="Q3" s="0">
         <v>0.0051308068533853692</v>
       </c>
-      <c r="P3" s="0">
+      <c r="R3" s="0">
+        <v>12.08788970370618</v>
+      </c>
+      <c r="S3" s="0">
+        <v>1.8090456838780643e-31</v>
+      </c>
+      <c r="T3" s="0">
         <v>-2.5654166979981485</v>
       </c>
-      <c r="Q3" s="0">
+      <c r="U3" s="0">
         <v>0.010422507845564739</v>
       </c>
-      <c r="R3" s="0">
+      <c r="V3" s="0">
         <v>0.64051901111620702</v>
       </c>
-      <c r="S3" s="0">
+      <c r="W3" s="0">
         <v>0.52248127082485785</v>
       </c>
-      <c r="T3" s="0">
+      <c r="X3" s="0">
         <v>15.094052856959351</v>
       </c>
-      <c r="U3" s="0">
+      <c r="Y3" s="0">
         <v>3.2720734313940406e-45</v>
       </c>
-      <c r="V3" s="0">
+      <c r="Z3" s="0">
         <v>-2.9830821597097414</v>
       </c>
-      <c r="W3" s="0">
+      <c r="AA3" s="0">
         <v>0.0031406381512496841</v>
       </c>
-      <c r="X3" s="0">
+      <c r="AB3" s="0">
+        <v>8.7955252592927309</v>
+      </c>
+      <c r="AC3" s="0">
+        <v>6.2457531693509853e-18</v>
+      </c>
+      <c r="AD3" s="0">
         <v>-2.821501030362656</v>
       </c>
-      <c r="Y3" s="0">
+      <c r="AE3" s="0">
         <v>0.0048565769653519299</v>
       </c>
     </row>
@@ -9372,66 +9436,84 @@
         <v>1.109256853839961</v>
       </c>
       <c r="E4" s="0">
+        <v>0.88207792451309053</v>
+      </c>
+      <c r="F4" s="0">
         <v>1.059623807170029</v>
       </c>
-      <c r="F4" s="0">
+      <c r="G4" s="0">
         <v>0.84933401690485932</v>
       </c>
-      <c r="G4" s="0">
+      <c r="H4" s="0">
         <v>0.62558073763468414</v>
       </c>
-      <c r="H4" s="0">
+      <c r="I4" s="0">
         <v>1.1000687253809462</v>
       </c>
-      <c r="I4" s="0">
+      <c r="J4" s="0">
+        <v>0.69403249286371405</v>
+      </c>
+      <c r="K4" s="0">
         <v>0.9313573051186832</v>
       </c>
-      <c r="J4" s="0">
+      <c r="L4" s="0">
         <v>3.5350755014421784</v>
       </c>
-      <c r="K4" s="0">
+      <c r="M4" s="0">
         <v>0.0004939800443412777</v>
       </c>
-      <c r="L4" s="0">
+      <c r="N4" s="0">
         <v>17.415998092629014</v>
       </c>
-      <c r="M4" s="0">
+      <c r="O4" s="0">
         <v>2.0929120267264281e-57</v>
       </c>
-      <c r="N4" s="0">
+      <c r="P4" s="0">
         <v>-1.8424749645216265</v>
       </c>
-      <c r="O4" s="0">
+      <c r="Q4" s="0">
         <v>0.066609069575434637</v>
       </c>
-      <c r="P4" s="0">
+      <c r="R4" s="0">
+        <v>14.076634906529454</v>
+      </c>
+      <c r="S4" s="0">
+        <v>3.7929898468030606e-41</v>
+      </c>
+      <c r="T4" s="0">
         <v>-1.486495599523854</v>
       </c>
-      <c r="Q4" s="0">
+      <c r="U4" s="0">
         <v>0.13740352220572905</v>
       </c>
-      <c r="R4" s="0">
+      <c r="V4" s="0">
         <v>1.5165771671272084</v>
       </c>
-      <c r="S4" s="0">
+      <c r="W4" s="0">
         <v>0.13076479881401026</v>
       </c>
-      <c r="T4" s="0">
+      <c r="X4" s="0">
         <v>14.347067058517595</v>
       </c>
-      <c r="U4" s="0">
+      <c r="Y4" s="0">
         <v>1.7632467530097052e-41</v>
       </c>
-      <c r="V4" s="0">
+      <c r="Z4" s="0">
         <v>-2.2158237362969633</v>
       </c>
-      <c r="W4" s="0">
+      <c r="AA4" s="0">
         <v>0.027619464489136568</v>
       </c>
-      <c r="X4" s="0">
+      <c r="AB4" s="0">
+        <v>9.6650691057140872</v>
+      </c>
+      <c r="AC4" s="0">
+        <v>3.5528434690560281e-21</v>
+      </c>
+      <c r="AD4" s="0">
         <v>-2.0193771577520128</v>
       </c>
-      <c r="Y4" s="0">
+      <c r="AE4" s="0">
         <v>0.043663881371493019</v>
       </c>
     </row>
@@ -9449,66 +9531,84 @@
         <v>1.0762372680821126</v>
       </c>
       <c r="E5" s="0">
+        <v>1.000888821362981</v>
+      </c>
+      <c r="F5" s="0">
         <v>1.0604115192875607</v>
       </c>
-      <c r="F5" s="0">
+      <c r="G5" s="0">
         <v>1.0872916389405003</v>
       </c>
-      <c r="G5" s="0">
+      <c r="H5" s="0">
         <v>0.77981418143840608</v>
       </c>
-      <c r="H5" s="0">
+      <c r="I5" s="0">
         <v>1.3301788362289793</v>
       </c>
-      <c r="I5" s="0">
+      <c r="J5" s="0">
+        <v>0.87387926834139484</v>
+      </c>
+      <c r="K5" s="0">
         <v>1.1405825834854408</v>
       </c>
-      <c r="J5" s="0">
+      <c r="L5" s="0">
         <v>-0.62616477149411554</v>
       </c>
-      <c r="K5" s="0">
+      <c r="M5" s="0">
         <v>0.53183598891693162</v>
       </c>
-      <c r="L5" s="0">
+      <c r="N5" s="0">
         <v>18.487473611459716</v>
       </c>
-      <c r="M5" s="0">
+      <c r="O5" s="0">
         <v>2.7529249436657225e-63</v>
       </c>
-      <c r="N5" s="0">
+      <c r="P5" s="0">
         <v>-2.7250507809586226</v>
       </c>
-      <c r="O5" s="0">
+      <c r="Q5" s="0">
         <v>0.0068908261007236682</v>
       </c>
-      <c r="P5" s="0">
+      <c r="R5" s="0">
+        <v>8.2566910574261776</v>
+      </c>
+      <c r="S5" s="0">
+        <v>4.771787731001723e-16</v>
+      </c>
+      <c r="T5" s="0">
         <v>-2.30957472588715</v>
       </c>
-      <c r="Q5" s="0">
+      <c r="U5" s="0">
         <v>0.021076152822258918</v>
       </c>
-      <c r="R5" s="0">
+      <c r="V5" s="0">
         <v>-1.7658698730945108</v>
       </c>
-      <c r="S5" s="0">
+      <c r="W5" s="0">
         <v>0.078761927332736542</v>
       </c>
-      <c r="T5" s="0">
+      <c r="X5" s="0">
         <v>11.848212354367849</v>
       </c>
-      <c r="U5" s="0">
+      <c r="Y5" s="0">
         <v>7.802559109319772e-30</v>
       </c>
-      <c r="V5" s="0">
+      <c r="Z5" s="0">
         <v>-4.5371347343910839</v>
       </c>
-      <c r="W5" s="0">
+      <c r="AA5" s="0">
         <v>8.9207505028757148e-06</v>
       </c>
-      <c r="X5" s="0">
+      <c r="AB5" s="0">
+        <v>3.8200215697891444</v>
+      </c>
+      <c r="AC5" s="0">
+        <v>0.00014177482368222846</v>
+      </c>
+      <c r="AD5" s="0">
         <v>-4.2762236088481478</v>
       </c>
-      <c r="Y5" s="0">
+      <c r="AE5" s="0">
         <v>2.0475124064199845e-05</v>
       </c>
     </row>
@@ -9526,66 +9626,84 @@
         <v>1.3528374652136588</v>
       </c>
       <c r="E6" s="0">
+        <v>1.0842387076993287</v>
+      </c>
+      <c r="F6" s="0">
         <v>1.2725634797741714</v>
       </c>
-      <c r="F6" s="0">
+      <c r="G6" s="0">
         <v>1.0108260890629996</v>
       </c>
-      <c r="G6" s="0">
+      <c r="H6" s="0">
         <v>0.54256726804718802</v>
       </c>
-      <c r="H6" s="0">
+      <c r="I6" s="0">
         <v>1.1634659339977795</v>
       </c>
-      <c r="I6" s="0">
+      <c r="J6" s="0">
+        <v>0.68581941748856101</v>
+      </c>
+      <c r="K6" s="0">
         <v>0.96499984715620035</v>
       </c>
-      <c r="J6" s="0">
+      <c r="L6" s="0">
         <v>-1.6732117962018269</v>
       </c>
-      <c r="K6" s="0">
+      <c r="M6" s="0">
         <v>0.095663082110970077</v>
       </c>
-      <c r="L6" s="0">
+      <c r="N6" s="0">
         <v>20.194059821885109</v>
       </c>
-      <c r="M6" s="0">
+      <c r="O6" s="0">
         <v>6.5388288180086506e-73</v>
       </c>
-      <c r="N6" s="0">
+      <c r="P6" s="0">
         <v>-3.3435006369195857</v>
       </c>
-      <c r="O6" s="0">
+      <c r="Q6" s="0">
         <v>0.00095630050802392153</v>
       </c>
-      <c r="P6" s="0">
+      <c r="R6" s="0">
+        <v>6.2673587693810981</v>
+      </c>
+      <c r="S6" s="0">
+        <v>5.4785475496191744e-10</v>
+      </c>
+      <c r="T6" s="0">
         <v>-3.1409811772482086</v>
       </c>
-      <c r="Q6" s="0">
+      <c r="U6" s="0">
         <v>0.0017238466204571353</v>
       </c>
-      <c r="R6" s="0">
+      <c r="V6" s="0">
         <v>-2.5193115892085225</v>
       </c>
-      <c r="S6" s="0">
+      <c r="W6" s="0">
         <v>0.012446850515668311</v>
       </c>
-      <c r="T6" s="0">
+      <c r="X6" s="0">
         <v>17.302923652071581</v>
       </c>
-      <c r="U6" s="0">
+      <c r="Y6" s="0">
         <v>8.5696541887444999e-57</v>
       </c>
-      <c r="V6" s="0">
+      <c r="Z6" s="0">
         <v>-3.5179422072061297</v>
       </c>
-      <c r="W6" s="0">
+      <c r="AA6" s="0">
         <v>0.00051785284638216874</v>
       </c>
-      <c r="X6" s="0">
+      <c r="AB6" s="0">
+        <v>3.5709578189175382</v>
+      </c>
+      <c r="AC6" s="0">
+        <v>0.00037283201256398612</v>
+      </c>
+      <c r="AD6" s="0">
         <v>-3.3892549903109761</v>
       </c>
-      <c r="Y6" s="0">
+      <c r="AE6" s="0">
         <v>0.00072295490928230423</v>
       </c>
     </row>
@@ -9603,66 +9721,84 @@
         <v>1.0722697764418421</v>
       </c>
       <c r="E7" s="0">
+        <v>1.0224710088097597</v>
+      </c>
+      <c r="F7" s="0">
         <v>1.0355472345714909</v>
       </c>
-      <c r="F7" s="0">
+      <c r="G7" s="0">
         <v>0.9093730075484644</v>
       </c>
-      <c r="G7" s="0">
+      <c r="H7" s="0">
         <v>0.6172702996233882</v>
       </c>
-      <c r="H7" s="0">
+      <c r="I7" s="0">
         <v>1.0245972809627573</v>
       </c>
-      <c r="I7" s="0">
+      <c r="J7" s="0">
+        <v>0.70663186397606459</v>
+      </c>
+      <c r="K7" s="0">
         <v>0.89248001457611525</v>
       </c>
-      <c r="J7" s="0">
+      <c r="L7" s="0">
         <v>0.56915791670150406</v>
       </c>
-      <c r="K7" s="0">
+      <c r="M7" s="0">
         <v>0.56981170083909705</v>
       </c>
-      <c r="L7" s="0">
+      <c r="N7" s="0">
         <v>20.020468590217426</v>
       </c>
-      <c r="M7" s="0">
+      <c r="O7" s="0">
         <v>6.4115894996648282e-72</v>
       </c>
-      <c r="N7" s="0">
+      <c r="P7" s="0">
         <v>-1.4337323006608715</v>
       </c>
-      <c r="O7" s="0">
+      <c r="Q7" s="0">
         <v>0.1529184760805854</v>
       </c>
-      <c r="P7" s="0">
+      <c r="R7" s="0">
+        <v>9.768289217907224</v>
+      </c>
+      <c r="S7" s="0">
+        <v>1.4089934286564663e-21</v>
+      </c>
+      <c r="T7" s="0">
         <v>-1.0237588642207562</v>
       </c>
-      <c r="Q7" s="0">
+      <c r="U7" s="0">
         <v>0.30614983131302509</v>
       </c>
-      <c r="R7" s="0">
+      <c r="V7" s="0">
         <v>-0.65534522218737434</v>
       </c>
-      <c r="S7" s="0">
+      <c r="W7" s="0">
         <v>0.51290909366994331</v>
       </c>
-      <c r="T7" s="0">
+      <c r="X7" s="0">
         <v>16.79734896352128</v>
       </c>
-      <c r="U7" s="0">
+      <c r="Y7" s="0">
         <v>4.4563373661408183e-54</v>
       </c>
-      <c r="V7" s="0">
+      <c r="Z7" s="0">
         <v>-1.7336863705397119</v>
       </c>
-      <c r="W7" s="0">
+      <c r="AA7" s="0">
         <v>0.084226647691495779</v>
       </c>
-      <c r="X7" s="0">
+      <c r="AB7" s="0">
+        <v>6.3806690436505162</v>
+      </c>
+      <c r="AC7" s="0">
+        <v>2.7067554966753452e-10</v>
+      </c>
+      <c r="AD7" s="0">
         <v>-1.5129378868801544</v>
       </c>
-      <c r="Y7" s="0">
+      <c r="AE7" s="0">
         <v>0.13055149241186959</v>
       </c>
     </row>
@@ -9680,66 +9816,84 @@
         <v>1.2572119826890082</v>
       </c>
       <c r="E8" s="0">
+        <v>1.1515883890954905</v>
+      </c>
+      <c r="F8" s="0">
         <v>1.2431541525375771</v>
       </c>
-      <c r="F8" s="0">
+      <c r="G8" s="0">
         <v>1.1715546681009421</v>
       </c>
-      <c r="G8" s="0">
+      <c r="H8" s="0">
         <v>0.62583272182630567</v>
       </c>
-      <c r="H8" s="0">
+      <c r="I8" s="0">
         <v>1.3260877207327531</v>
       </c>
-      <c r="I8" s="0">
+      <c r="J8" s="0">
+        <v>0.79278278937993218</v>
+      </c>
+      <c r="K8" s="0">
         <v>1.1044951011687232</v>
       </c>
-      <c r="J8" s="0">
+      <c r="L8" s="0">
         <v>-3.0177638030366958</v>
       </c>
-      <c r="K8" s="0">
+      <c r="M8" s="0">
         <v>0.002837090933937999</v>
       </c>
-      <c r="L8" s="0">
+      <c r="N8" s="0">
         <v>19.218286354842636</v>
       </c>
-      <c r="M8" s="0">
+      <c r="O8" s="0">
         <v>2.2564580705225537e-67</v>
       </c>
-      <c r="N8" s="0">
+      <c r="P8" s="0">
         <v>-4.7897580811278759</v>
       </c>
-      <c r="O8" s="0">
+      <c r="Q8" s="0">
         <v>2.8873601324469906e-06</v>
       </c>
-      <c r="P8" s="0">
+      <c r="R8" s="0">
+        <v>3.4362688798516472</v>
+      </c>
+      <c r="S8" s="0">
+        <v>0.00061436802741540676</v>
+      </c>
+      <c r="T8" s="0">
         <v>-4.4061084217724797</v>
       </c>
-      <c r="Q8" s="0">
+      <c r="U8" s="0">
         <v>1.1437834076202683e-05</v>
       </c>
-      <c r="R8" s="0">
+      <c r="V8" s="0">
         <v>-4.0636805092941239</v>
       </c>
-      <c r="S8" s="0">
+      <c r="W8" s="0">
         <v>6.6581100067583985e-05</v>
       </c>
-      <c r="T8" s="0">
+      <c r="X8" s="0">
         <v>15.040280487910088</v>
       </c>
-      <c r="U8" s="0">
+      <c r="Y8" s="0">
         <v>6.12144866788945e-45</v>
       </c>
-      <c r="V8" s="0">
+      <c r="Z8" s="0">
         <v>-5.2182349318723702</v>
       </c>
-      <c r="W8" s="0">
+      <c r="AA8" s="0">
         <v>3.8389013970344509e-07</v>
       </c>
-      <c r="X8" s="0">
+      <c r="AB8" s="0">
+        <v>0.60532415200886813</v>
+      </c>
+      <c r="AC8" s="0">
+        <v>0.54510278968066261</v>
+      </c>
+      <c r="AD8" s="0">
         <v>-4.9816780491150743</v>
       </c>
-      <c r="Y8" s="0">
+      <c r="AE8" s="0">
         <v>7.1996974808938764e-07</v>
       </c>
     </row>
@@ -9757,66 +9911,84 @@
         <v>1.0700986728557147</v>
       </c>
       <c r="E9" s="0">
+        <v>0.95437927623600427</v>
+      </c>
+      <c r="F9" s="0">
         <v>1.0278927212747475</v>
       </c>
-      <c r="F9" s="0">
+      <c r="G9" s="0">
         <v>0.82118782475167629</v>
       </c>
-      <c r="G9" s="0">
+      <c r="H9" s="0">
         <v>0.76238825723686843</v>
       </c>
-      <c r="H9" s="0">
+      <c r="I9" s="0">
         <v>1.0827699129399924</v>
       </c>
-      <c r="I9" s="0">
+      <c r="J9" s="0">
+        <v>0.78037652367132992</v>
+      </c>
+      <c r="K9" s="0">
         <v>0.95712295314738249</v>
       </c>
-      <c r="J9" s="0">
+      <c r="L9" s="0">
         <v>5.1595717787187327</v>
       </c>
-      <c r="K9" s="0">
+      <c r="M9" s="0">
         <v>5.393974997827873e-07</v>
       </c>
-      <c r="L9" s="0">
+      <c r="N9" s="0">
         <v>11.697448158921643</v>
       </c>
-      <c r="M9" s="0">
+      <c r="O9" s="0">
         <v>3.5372985686989672e-29</v>
       </c>
-      <c r="N9" s="0">
+      <c r="P9" s="0">
         <v>-1.4448116762828545</v>
       </c>
-      <c r="O9" s="0">
+      <c r="Q9" s="0">
         <v>0.14978333205181149</v>
       </c>
-      <c r="P9" s="0">
+      <c r="R9" s="0">
+        <v>12.440251320624409</v>
+      </c>
+      <c r="S9" s="0">
+        <v>4.1518304453127247e-33</v>
+      </c>
+      <c r="T9" s="0">
         <v>-1.1391677652623113</v>
       </c>
-      <c r="Q9" s="0">
+      <c r="U9" s="0">
         <v>0.25485427288367957</v>
       </c>
-      <c r="R9" s="0">
+      <c r="V9" s="0">
         <v>2.2296530382675059</v>
       </c>
-      <c r="S9" s="0">
+      <c r="W9" s="0">
         <v>0.026749649764363899</v>
       </c>
-      <c r="T9" s="0">
+      <c r="X9" s="0">
         <v>9.3428758016199556</v>
       </c>
-      <c r="U9" s="0">
+      <c r="Y9" s="0">
         <v>1.0196980266929119e-19</v>
       </c>
-      <c r="V9" s="0">
+      <c r="Z9" s="0">
         <v>-1.6431115377615733</v>
       </c>
-      <c r="W9" s="0">
+      <c r="AA9" s="0">
         <v>0.10163736410998303</v>
       </c>
-      <c r="X9" s="0">
+      <c r="AB9" s="0">
+        <v>8.3697321118144732</v>
+      </c>
+      <c r="AC9" s="0">
+        <v>1.9584284474260183e-16</v>
+      </c>
+      <c r="AD9" s="0">
         <v>-1.4853440265822007</v>
       </c>
-      <c r="Y9" s="0">
+      <c r="AE9" s="0">
         <v>0.13770812358957452</v>
       </c>
     </row>
@@ -9834,66 +10006,84 @@
         <v>1.1695369769476156</v>
       </c>
       <c r="E10" s="0">
+        <v>0.91707026640165956</v>
+      </c>
+      <c r="F10" s="0">
         <v>1.1049330237073789</v>
       </c>
-      <c r="F10" s="0">
+      <c r="G10" s="0">
         <v>0.88762465800329915</v>
       </c>
-      <c r="G10" s="0">
+      <c r="H10" s="0">
         <v>0.68870271615163303</v>
       </c>
-      <c r="H10" s="0">
+      <c r="I10" s="0">
         <v>1.184062619535597</v>
       </c>
-      <c r="I10" s="0">
+      <c r="J10" s="0">
+        <v>0.74955794078890847</v>
+      </c>
+      <c r="K10" s="0">
         <v>1.0035223238888507</v>
       </c>
-      <c r="J10" s="0">
+      <c r="L10" s="0">
         <v>3.8307971856425667</v>
       </c>
-      <c r="K10" s="0">
+      <c r="M10" s="0">
         <v>0.00016533137730559251</v>
       </c>
-      <c r="L10" s="0">
+      <c r="N10" s="0">
         <v>15.192266929704246</v>
       </c>
-      <c r="M10" s="0">
+      <c r="O10" s="0">
         <v>1.0390585315469462e-45</v>
       </c>
-      <c r="N10" s="0">
+      <c r="P10" s="0">
         <v>-2.4185002792442529</v>
       </c>
-      <c r="O10" s="0">
+      <c r="Q10" s="0">
         <v>0.016311549327115909</v>
       </c>
-      <c r="P10" s="0">
+      <c r="R10" s="0">
+        <v>13.038712205857243</v>
+      </c>
+      <c r="S10" s="0">
+        <v>5.7228080615303891e-36</v>
+      </c>
+      <c r="T10" s="0">
         <v>-2.017023520643519</v>
       </c>
-      <c r="Q10" s="0">
+      <c r="U10" s="0">
         <v>0.043909275017315383</v>
       </c>
-      <c r="R10" s="0">
+      <c r="V10" s="0">
         <v>1.0650715712336345</v>
       </c>
-      <c r="S10" s="0">
+      <c r="W10" s="0">
         <v>0.28797510919959457</v>
       </c>
-      <c r="T10" s="0">
+      <c r="X10" s="0">
         <v>11.731299547947216</v>
       </c>
-      <c r="U10" s="0">
+      <c r="Y10" s="0">
         <v>2.5221876886517191e-29</v>
       </c>
-      <c r="V10" s="0">
+      <c r="Z10" s="0">
         <v>-2.6754808477984398</v>
       </c>
-      <c r="W10" s="0">
+      <c r="AA10" s="0">
         <v>0.0079631790226944044</v>
       </c>
-      <c r="X10" s="0">
+      <c r="AB10" s="0">
+        <v>7.9448844327153676</v>
+      </c>
+      <c r="AC10" s="0">
+        <v>5.2777562882893566e-15</v>
+      </c>
+      <c r="AD10" s="0">
         <v>-2.4739960074419516</v>
       </c>
-      <c r="Y10" s="0">
+      <c r="AE10" s="0">
         <v>0.013494841805516983</v>
       </c>
     </row>
@@ -9911,66 +10101,84 @@
         <v>1.260037701181234</v>
       </c>
       <c r="E11" s="0">
+        <v>0.87691277324567374</v>
+      </c>
+      <c r="F11" s="0">
         <v>1.1802895327747147</v>
       </c>
-      <c r="F11" s="0">
+      <c r="G11" s="0">
         <v>1.3873336674412862</v>
       </c>
-      <c r="G11" s="0">
+      <c r="H11" s="0">
         <v>1.1319432215575471</v>
       </c>
-      <c r="H11" s="0">
+      <c r="I11" s="0">
         <v>1.261673060062686</v>
       </c>
-      <c r="I11" s="0">
+      <c r="J11" s="0">
+        <v>1.2100735816867396</v>
+      </c>
+      <c r="K11" s="0">
         <v>1.2402330490872409</v>
       </c>
-      <c r="J11" s="0">
+      <c r="L11" s="0">
         <v>2.4082131835004676</v>
       </c>
-      <c r="K11" s="0">
+      <c r="M11" s="0">
         <v>0.016829461493427587</v>
       </c>
-      <c r="L11" s="0">
+      <c r="N11" s="0">
         <v>16.423778596485395</v>
       </c>
-      <c r="M11" s="0">
+      <c r="O11" s="0">
         <v>4.2899544896502455e-52</v>
       </c>
-      <c r="N11" s="0">
+      <c r="P11" s="0">
         <v>-2.8936367470361608</v>
       </c>
-      <c r="O11" s="0">
+      <c r="Q11" s="0">
         <v>0.0041497088136781728</v>
       </c>
-      <c r="P11" s="0">
+      <c r="R11" s="0">
+        <v>12.586108378638988</v>
+      </c>
+      <c r="S11" s="0">
+        <v>8.5078323534146209e-34</v>
+      </c>
+      <c r="T11" s="0">
         <v>-2.6235724160144676</v>
       </c>
-      <c r="Q11" s="0">
+      <c r="U11" s="0">
         <v>0.0088086029675560912</v>
       </c>
-      <c r="R11" s="0">
+      <c r="V11" s="0">
         <v>-5.0120677489492458</v>
       </c>
-      <c r="S11" s="0">
+      <c r="W11" s="0">
         <v>1.0835870512660321e-06</v>
       </c>
-      <c r="T11" s="0">
+      <c r="X11" s="0">
         <v>1.1851149541187005</v>
       </c>
-      <c r="U11" s="0">
+      <c r="Y11" s="0">
         <v>0.23634292452826011</v>
       </c>
-      <c r="V11" s="0">
+      <c r="Z11" s="0">
         <v>-3.096381817117388</v>
       </c>
-      <c r="W11" s="0">
+      <c r="AA11" s="0">
         <v>0.0021859771049803985</v>
       </c>
-      <c r="X11" s="0">
+      <c r="AB11" s="0">
+        <v>-3.1121353044613032</v>
+      </c>
+      <c r="AC11" s="0">
+        <v>0.0019108136768143532</v>
+      </c>
+      <c r="AD11" s="0">
         <v>-3.1156122027381037</v>
       </c>
-      <c r="Y11" s="0">
+      <c r="AE11" s="0">
         <v>0.0018779697102112986</v>
       </c>
     </row>
@@ -9988,66 +10196,84 @@
         <v>1.045811054115052</v>
       </c>
       <c r="E12" s="0">
+        <v>0.89205031562240589</v>
+      </c>
+      <c r="F12" s="0">
         <v>1.0197316502560871</v>
       </c>
-      <c r="F12" s="0">
+      <c r="G12" s="0">
         <v>2.3564411028048586</v>
       </c>
-      <c r="G12" s="0">
+      <c r="H12" s="0">
         <v>2.6793356426573274</v>
       </c>
-      <c r="H12" s="0">
+      <c r="I12" s="0">
         <v>1.7567053190552606</v>
       </c>
-      <c r="I12" s="0">
+      <c r="J12" s="0">
+        <v>2.5805540825440425</v>
+      </c>
+      <c r="K12" s="0">
         <v>2.099021309201786</v>
       </c>
-      <c r="J12" s="0">
+      <c r="L12" s="0">
         <v>4.5566968010106272</v>
       </c>
-      <c r="K12" s="0">
+      <c r="M12" s="0">
         <v>8.4879340229886082e-06</v>
       </c>
-      <c r="L12" s="0">
+      <c r="N12" s="0">
         <v>15.087926963892571</v>
       </c>
-      <c r="M12" s="0">
+      <c r="O12" s="0">
         <v>3.5143058794066294e-45</v>
       </c>
-      <c r="N12" s="0">
+      <c r="P12" s="0">
         <v>-1.592648900195281</v>
       </c>
-      <c r="O12" s="0">
+      <c r="Q12" s="0">
         <v>0.11252306531283163</v>
       </c>
-      <c r="P12" s="0">
+      <c r="R12" s="0">
+        <v>14.095126135308854</v>
+      </c>
+      <c r="S12" s="0">
+        <v>3.0501946296453481e-41</v>
+      </c>
+      <c r="T12" s="0">
         <v>-1.2326893956846769</v>
       </c>
-      <c r="Q12" s="0">
+      <c r="U12" s="0">
         <v>0.21792646108173963</v>
       </c>
-      <c r="R12" s="0">
+      <c r="V12" s="0">
         <v>-24.096681338029146</v>
       </c>
-      <c r="S12" s="0">
+      <c r="W12" s="0">
         <v>1.7118418891332816e-64</v>
       </c>
-      <c r="T12" s="0">
+      <c r="X12" s="0">
         <v>-42.878720704661582</v>
       </c>
-      <c r="U12" s="0">
+      <c r="Y12" s="0">
         <v>5.7415704412546425e-205</v>
       </c>
-      <c r="V12" s="0">
+      <c r="Z12" s="0">
         <v>-1.9045606602859595</v>
       </c>
-      <c r="W12" s="0">
+      <c r="AA12" s="0">
         <v>0.05800366414186834</v>
       </c>
-      <c r="X12" s="0">
+      <c r="AB12" s="0">
+        <v>-46.213619790465934</v>
+      </c>
+      <c r="AC12" s="0">
+        <v>4.2843616940807039e-249</v>
+      </c>
+      <c r="AD12" s="0">
         <v>-2.1379889835773644</v>
       </c>
-      <c r="Y12" s="0">
+      <c r="AE12" s="0">
         <v>0.032713622988191499</v>
       </c>
     </row>
@@ -10065,66 +10291,84 @@
         <v>1.23205796898611</v>
       </c>
       <c r="E13" s="0">
+        <v>0.89251695985054103</v>
+      </c>
+      <c r="F13" s="0">
         <v>1.1564347076470733</v>
       </c>
-      <c r="F13" s="0">
+      <c r="G13" s="0">
         <v>0.94785621256402319</v>
       </c>
-      <c r="G13" s="0">
+      <c r="H13" s="0">
         <v>0.70183104337817048</v>
       </c>
-      <c r="H13" s="0">
+      <c r="I13" s="0">
         <v>1.2406071403634642</v>
       </c>
-      <c r="I13" s="0">
+      <c r="J13" s="0">
+        <v>0.77709632984110466</v>
+      </c>
+      <c r="K13" s="0">
         <v>1.0480145565308843</v>
       </c>
-      <c r="J13" s="0">
+      <c r="L13" s="0">
         <v>2.1881292945307633</v>
       </c>
-      <c r="K13" s="0">
+      <c r="M13" s="0">
         <v>0.029680403210347591</v>
       </c>
-      <c r="L13" s="0">
+      <c r="N13" s="0">
         <v>16.816350658088467</v>
       </c>
-      <c r="M13" s="0">
+      <c r="O13" s="0">
         <v>3.5281362370934081e-54</v>
       </c>
-      <c r="N13" s="0">
+      <c r="P13" s="0">
         <v>-2.6517131964540681</v>
       </c>
-      <c r="O13" s="0">
+      <c r="Q13" s="0">
         <v>0.0085288490635758458</v>
       </c>
-      <c r="P13" s="0">
+      <c r="R13" s="0">
+        <v>12.041360449290961</v>
+      </c>
+      <c r="S13" s="0">
+        <v>2.9603923233721189e-31</v>
+      </c>
+      <c r="T13" s="0">
         <v>-2.4094350700401073</v>
       </c>
-      <c r="Q13" s="0">
+      <c r="U13" s="0">
         <v>0.016122917521086393</v>
       </c>
-      <c r="R13" s="0">
+      <c r="V13" s="0">
         <v>0.40923648763887416</v>
       </c>
-      <c r="S13" s="0">
+      <c r="W13" s="0">
         <v>0.68275198327897335</v>
       </c>
-      <c r="T13" s="0">
+      <c r="X13" s="0">
         <v>12.32215762464355</v>
       </c>
-      <c r="U13" s="0">
+      <c r="Y13" s="0">
         <v>6.1970179193614661e-32</v>
       </c>
-      <c r="V13" s="0">
+      <c r="Z13" s="0">
         <v>-2.9013259502715187</v>
       </c>
-      <c r="W13" s="0">
+      <c r="AA13" s="0">
         <v>0.0040525503191495638</v>
       </c>
-      <c r="X13" s="0">
+      <c r="AB13" s="0">
+        <v>7.5338999608227972</v>
+      </c>
+      <c r="AC13" s="0">
+        <v>1.1111980385174405e-13</v>
+      </c>
+      <c r="AD13" s="0">
         <v>-2.7172166055015721</v>
       </c>
-      <c r="Y13" s="0">
+      <c r="AE13" s="0">
         <v>0.0066754417866877738</v>
       </c>
     </row>
@@ -10142,66 +10386,84 @@
         <v>1.2844817616151032</v>
       </c>
       <c r="E14" s="0">
+        <v>0.95099814534312144</v>
+      </c>
+      <c r="F14" s="0">
         <v>1.2041930062712984</v>
       </c>
-      <c r="F14" s="0">
+      <c r="G14" s="0">
         <v>0.96589103536892951</v>
       </c>
-      <c r="G14" s="0">
+      <c r="H14" s="0">
         <v>0.63588063589038812</v>
       </c>
-      <c r="H14" s="0">
+      <c r="I14" s="0">
         <v>1.2570333694054745</v>
       </c>
-      <c r="I14" s="0">
+      <c r="J14" s="0">
+        <v>0.73683911641778621</v>
+      </c>
+      <c r="K14" s="0">
         <v>1.0408883453771198</v>
       </c>
-      <c r="J14" s="0">
+      <c r="L14" s="0">
         <v>0.25764648055091449</v>
       </c>
-      <c r="K14" s="0">
+      <c r="M14" s="0">
         <v>0.79691316647131505</v>
       </c>
-      <c r="L14" s="0">
+      <c r="N14" s="0">
         <v>16.862866128992181</v>
       </c>
-      <c r="M14" s="0">
+      <c r="O14" s="0">
         <v>1.9907840017718365e-54</v>
       </c>
-      <c r="N14" s="0">
+      <c r="P14" s="0">
         <v>-2.9682944155749547</v>
       </c>
-      <c r="O14" s="0">
+      <c r="Q14" s="0">
         <v>0.0032901822914852613</v>
       </c>
-      <c r="P14" s="0">
+      <c r="R14" s="0">
+        <v>9.2026358189929809</v>
+      </c>
+      <c r="S14" s="0">
+        <v>2.0299822931166794e-19</v>
+      </c>
+      <c r="T14" s="0">
         <v>-2.7437769348034262</v>
       </c>
-      <c r="Q14" s="0">
+      <c r="U14" s="0">
         <v>0.0061616767052310572</v>
       </c>
-      <c r="R14" s="0">
+      <c r="V14" s="0">
         <v>-0.5711523921493743</v>
       </c>
-      <c r="S14" s="0">
+      <c r="W14" s="0">
         <v>0.5684613686812573</v>
       </c>
-      <c r="T14" s="0">
+      <c r="X14" s="0">
         <v>13.356450433388128</v>
       </c>
-      <c r="U14" s="0">
+      <c r="Y14" s="0">
         <v>1.0634248719828969e-36</v>
       </c>
-      <c r="V14" s="0">
+      <c r="Z14" s="0">
         <v>-3.2154453515173524</v>
       </c>
-      <c r="W14" s="0">
+      <c r="AA14" s="0">
         <v>0.0014768895038691165</v>
       </c>
-      <c r="X14" s="0">
+      <c r="AB14" s="0">
+        <v>6.6986063104949203</v>
+      </c>
+      <c r="AC14" s="0">
+        <v>3.5288590402632724e-11</v>
+      </c>
+      <c r="AD14" s="0">
         <v>-3.0194784571890851</v>
       </c>
-      <c r="Y14" s="0">
+      <c r="AE14" s="0">
         <v>0.0025841203402938678</v>
       </c>
     </row>
@@ -10219,66 +10481,84 @@
         <v>0.99946367727861329</v>
       </c>
       <c r="E15" s="0">
+        <v>0.86901510337002152</v>
+      </c>
+      <c r="F15" s="0">
         <v>0.96996126010735662</v>
       </c>
-      <c r="F15" s="0">
+      <c r="G15" s="0">
         <v>0.89449292940387071</v>
       </c>
-      <c r="G15" s="0">
+      <c r="H15" s="0">
         <v>0.6910836518007385</v>
       </c>
-      <c r="H15" s="0">
+      <c r="I15" s="0">
         <v>1.3279337348441118</v>
       </c>
-      <c r="I15" s="0">
+      <c r="J15" s="0">
+        <v>0.75331166529497184</v>
+      </c>
+      <c r="K15" s="0">
         <v>1.0891735018800204</v>
       </c>
-      <c r="J15" s="0">
+      <c r="L15" s="0">
         <v>3.978537410210504</v>
       </c>
-      <c r="K15" s="0">
+      <c r="M15" s="0">
         <v>9.3293607656749452e-05</v>
       </c>
-      <c r="L15" s="0">
+      <c r="N15" s="0">
         <v>17.120422092088226</v>
       </c>
-      <c r="M15" s="0">
+      <c r="O15" s="0">
         <v>8.2690265075149043e-56</v>
       </c>
-      <c r="N15" s="0">
+      <c r="P15" s="0">
         <v>-0.56597241866536618</v>
       </c>
-      <c r="O15" s="0">
+      <c r="Q15" s="0">
         <v>0.57192843733776377</v>
       </c>
-      <c r="P15" s="0">
+      <c r="R15" s="0">
+        <v>14.364000540583469</v>
+      </c>
+      <c r="S15" s="0">
+        <v>1.255637467329658e-42</v>
+      </c>
+      <c r="T15" s="0">
         <v>-0.14972975321907764</v>
       </c>
-      <c r="Q15" s="0">
+      <c r="U15" s="0">
         <v>0.88100230058208395</v>
       </c>
-      <c r="R15" s="0">
+      <c r="V15" s="0">
         <v>1.2447254998681763</v>
       </c>
-      <c r="S15" s="0">
+      <c r="W15" s="0">
         <v>0.21451620344795552</v>
       </c>
-      <c r="T15" s="0">
+      <c r="X15" s="0">
         <v>13.106369575954389</v>
       </c>
-      <c r="U15" s="0">
+      <c r="Y15" s="0">
         <v>1.5884602634112716e-35</v>
       </c>
-      <c r="V15" s="0">
+      <c r="Z15" s="0">
         <v>-2.1732547149901267</v>
       </c>
-      <c r="W15" s="0">
+      <c r="AA15" s="0">
         <v>0.030715656175449017</v>
       </c>
-      <c r="X15" s="0">
+      <c r="AB15" s="0">
+        <v>8.7005813064625919</v>
+      </c>
+      <c r="AC15" s="0">
+        <v>1.363329979060167e-17</v>
+      </c>
+      <c r="AD15" s="0">
         <v>-2.0952024443744381</v>
       </c>
-      <c r="Y15" s="0">
+      <c r="AE15" s="0">
         <v>0.036356411562443985</v>
       </c>
     </row>
@@ -10296,66 +10576,84 @@
         <v>1.3336847786330694</v>
       </c>
       <c r="E16" s="0">
+        <v>0.97506334756885726</v>
+      </c>
+      <c r="F16" s="0">
         <v>1.263539098253361</v>
       </c>
-      <c r="F16" s="0">
+      <c r="G16" s="0">
         <v>1.2103023264636434</v>
       </c>
-      <c r="G16" s="0">
+      <c r="H16" s="0">
         <v>1.412524352889611</v>
       </c>
-      <c r="H16" s="0">
+      <c r="I16" s="0">
         <v>1.2209517344425485</v>
       </c>
-      <c r="I16" s="0">
+      <c r="J16" s="0">
+        <v>1.3506595493882754</v>
+      </c>
+      <c r="K16" s="0">
         <v>1.2748464067060128</v>
       </c>
-      <c r="J16" s="0">
+      <c r="L16" s="0">
         <v>2.5029695267047183</v>
       </c>
-      <c r="K16" s="0">
+      <c r="M16" s="0">
         <v>0.013019942362077449</v>
       </c>
-      <c r="L16" s="0">
+      <c r="N16" s="0">
         <v>7.6524770845986865</v>
       </c>
-      <c r="M16" s="0">
+      <c r="O16" s="0">
         <v>5.9909890201443257e-14</v>
       </c>
-      <c r="N16" s="0">
+      <c r="P16" s="0">
         <v>-3.4410318956849295</v>
       </c>
-      <c r="O16" s="0">
+      <c r="Q16" s="0">
         <v>0.00068071650991420693</v>
       </c>
-      <c r="P16" s="0">
+      <c r="R16" s="0">
+        <v>7.0386248153199364</v>
+      </c>
+      <c r="S16" s="0">
+        <v>3.6304314201859328e-12</v>
+      </c>
+      <c r="T16" s="0">
         <v>-3.2218183427436267</v>
       </c>
-      <c r="Q16" s="0">
+      <c r="U16" s="0">
         <v>0.0013070700369382164</v>
       </c>
-      <c r="R16" s="0">
+      <c r="V16" s="0">
         <v>-2.2655208041577373</v>
       </c>
-      <c r="S16" s="0">
+      <c r="W16" s="0">
         <v>0.024423943999833667</v>
       </c>
-      <c r="T16" s="0">
+      <c r="X16" s="0">
         <v>-9.7290909422953202</v>
       </c>
-      <c r="U16" s="0">
+      <c r="Y16" s="0">
         <v>3.6713879119849687e-21</v>
       </c>
-      <c r="V16" s="0">
+      <c r="Z16" s="0">
         <v>-3.7053759779091009</v>
       </c>
-      <c r="W16" s="0">
+      <c r="AA16" s="0">
         <v>0.00026072792695402334</v>
       </c>
-      <c r="X16" s="0">
+      <c r="AB16" s="0">
+        <v>-8.1339687541256094</v>
+      </c>
+      <c r="AC16" s="0">
+        <v>1.2403695516489391e-15</v>
+      </c>
+      <c r="AD16" s="0">
         <v>-3.7921761698256753</v>
       </c>
-      <c r="Y16" s="0">
+      <c r="AE16" s="0">
         <v>0.00015655649418548623</v>
       </c>
     </row>
@@ -10373,66 +10671,84 @@
         <v>1.4221457287922821</v>
       </c>
       <c r="E17" s="0">
+        <v>1.0534560301723008</v>
+      </c>
+      <c r="F17" s="0">
         <v>1.3545126912331396</v>
       </c>
-      <c r="F17" s="0">
+      <c r="G17" s="0">
         <v>1.2148653839710444</v>
       </c>
-      <c r="G17" s="0">
+      <c r="H17" s="0">
         <v>1.366387693981955</v>
       </c>
-      <c r="H17" s="0">
+      <c r="I17" s="0">
         <v>1.2361698676369586</v>
       </c>
-      <c r="I17" s="0">
+      <c r="J17" s="0">
+        <v>1.3200332087630802</v>
+      </c>
+      <c r="K17" s="0">
         <v>1.2710157810216121</v>
       </c>
-      <c r="J17" s="0">
+      <c r="L17" s="0">
         <v>0.79402401794255439</v>
       </c>
-      <c r="K17" s="0">
+      <c r="M17" s="0">
         <v>0.42801071756263354</v>
       </c>
-      <c r="L17" s="0">
+      <c r="N17" s="0">
         <v>-0.93102736728633351</v>
       </c>
-      <c r="M17" s="0">
+      <c r="O17" s="0">
         <v>0.35213544041541067</v>
       </c>
-      <c r="N17" s="0">
+      <c r="P17" s="0">
         <v>-2.2873695611938301</v>
       </c>
-      <c r="O17" s="0">
+      <c r="Q17" s="0">
         <v>0.023023869049180166</v>
       </c>
-      <c r="P17" s="0">
+      <c r="R17" s="0">
+        <v>-0.34091832871794248</v>
+      </c>
+      <c r="S17" s="0">
+        <v>0.73323762110350943</v>
+      </c>
+      <c r="T17" s="0">
         <v>-2.2785935480318105</v>
       </c>
-      <c r="Q17" s="0">
+      <c r="U17" s="0">
         <v>0.022861498198200443</v>
       </c>
-      <c r="R17" s="0">
+      <c r="V17" s="0">
         <v>-3.2134344774309476</v>
       </c>
-      <c r="S17" s="0">
+      <c r="W17" s="0">
         <v>0.001502092695291336</v>
       </c>
-      <c r="T17" s="0">
+      <c r="X17" s="0">
         <v>-7.3653814492408918</v>
       </c>
-      <c r="U17" s="0">
+      <c r="Y17" s="0">
         <v>4.6120875533164474e-13</v>
       </c>
-      <c r="V17" s="0">
+      <c r="Z17" s="0">
         <v>-2.3110978517470184</v>
       </c>
-      <c r="W17" s="0">
+      <c r="AA17" s="0">
         <v>0.021654855985717869</v>
       </c>
-      <c r="X17" s="0">
+      <c r="AB17" s="0">
+        <v>-7.9157014971172028</v>
+      </c>
+      <c r="AC17" s="0">
+        <v>6.5825249068937373e-15</v>
+      </c>
+      <c r="AD17" s="0">
         <v>-2.3611617201350885</v>
       </c>
-      <c r="Y17" s="0">
+      <c r="AE17" s="0">
         <v>0.018372516625707123</v>
       </c>
     </row>
@@ -10450,66 +10766,84 @@
         <v>1.5436133298768002</v>
       </c>
       <c r="E18" s="0">
+        <v>1.0735163744012535</v>
+      </c>
+      <c r="F18" s="0">
         <v>1.4398101971452426</v>
       </c>
-      <c r="F18" s="0">
+      <c r="G18" s="0">
         <v>1.1714913688729778</v>
       </c>
-      <c r="G18" s="0">
+      <c r="H18" s="0">
         <v>0.8317169203307988</v>
       </c>
-      <c r="H18" s="0">
+      <c r="I18" s="0">
         <v>1.2840770165980766</v>
       </c>
-      <c r="I18" s="0">
+      <c r="J18" s="0">
+        <v>0.93566246901973804</v>
+      </c>
+      <c r="K18" s="0">
         <v>1.1393078840564854</v>
       </c>
-      <c r="J18" s="0">
+      <c r="L18" s="0">
         <v>-0.77049722032791435</v>
       </c>
-      <c r="K18" s="0">
+      <c r="M18" s="0">
         <v>0.44180616135515705</v>
       </c>
-      <c r="L18" s="0">
+      <c r="N18" s="0">
         <v>10.55868641610911</v>
       </c>
-      <c r="M18" s="0">
+      <c r="O18" s="0">
         <v>2.0716956284015153e-24</v>
       </c>
-      <c r="N18" s="0">
+      <c r="P18" s="0">
         <v>-4.9136156771471073</v>
       </c>
-      <c r="O18" s="0">
+      <c r="Q18" s="0">
         <v>1.6329891444256898e-06</v>
       </c>
-      <c r="P18" s="0">
+      <c r="R18" s="0">
+        <v>4.2936110118742965</v>
+      </c>
+      <c r="S18" s="0">
+        <v>1.9313604938337866e-05</v>
+      </c>
+      <c r="T18" s="0">
         <v>-4.6336009299424443</v>
       </c>
-      <c r="Q18" s="0">
+      <c r="U18" s="0">
         <v>3.9747077712025626e-06</v>
       </c>
-      <c r="R18" s="0">
+      <c r="V18" s="0">
         <v>-2.4778540849054749</v>
       </c>
-      <c r="S18" s="0">
+      <c r="W18" s="0">
         <v>0.013946551323921072</v>
       </c>
-      <c r="T18" s="0">
+      <c r="X18" s="0">
         <v>7.1873101479769153</v>
       </c>
-      <c r="U18" s="0">
+      <c r="Y18" s="0">
         <v>1.5830206787771674e-12</v>
       </c>
-      <c r="V18" s="0">
+      <c r="Z18" s="0">
         <v>-5.0692608902360989</v>
       </c>
-      <c r="W18" s="0">
+      <c r="AA18" s="0">
         <v>7.8565363591311846e-07</v>
       </c>
-      <c r="X18" s="0">
+      <c r="AB18" s="0">
+        <v>0.56793932483688148</v>
+      </c>
+      <c r="AC18" s="0">
+        <v>0.5702053390412678</v>
+      </c>
+      <c r="AD18" s="0">
         <v>-4.871538474226262</v>
       </c>
-      <c r="Y18" s="0">
+      <c r="AE18" s="0">
         <v>1.2510467217140169e-06</v>
       </c>
     </row>
@@ -10527,66 +10861,84 @@
         <v>1.8667535930846255</v>
       </c>
       <c r="E19" s="0">
+        <v>0.92208774721112907</v>
+      </c>
+      <c r="F19" s="0">
         <v>1.7315276982138148</v>
       </c>
-      <c r="F19" s="0">
+      <c r="G19" s="0">
         <v>0.83405660369106838</v>
       </c>
-      <c r="G19" s="0">
+      <c r="H19" s="0">
         <v>0.50472525782180233</v>
       </c>
-      <c r="H19" s="0">
+      <c r="I19" s="0">
         <v>1.477532403556612</v>
       </c>
-      <c r="I19" s="0">
+      <c r="J19" s="0">
+        <v>0.60547599877281955</v>
+      </c>
+      <c r="K19" s="0">
         <v>1.1151857388568489</v>
       </c>
-      <c r="J19" s="0">
+      <c r="L19" s="0">
         <v>3.8486980494579965</v>
       </c>
-      <c r="K19" s="0">
+      <c r="M19" s="0">
         <v>0.00015439499338517376</v>
       </c>
-      <c r="L19" s="0">
+      <c r="N19" s="0">
         <v>15.487900586072763</v>
       </c>
-      <c r="M19" s="0">
+      <c r="O19" s="0">
         <v>3.2130392392335081e-47</v>
       </c>
-      <c r="N19" s="0">
+      <c r="P19" s="0">
         <v>-4.8005969723707542</v>
       </c>
-      <c r="O19" s="0">
+      <c r="Q19" s="0">
         <v>2.7480916056502332e-06</v>
       </c>
-      <c r="P19" s="0">
+      <c r="R19" s="0">
+        <v>13.730788755088858</v>
+      </c>
+      <c r="S19" s="0">
+        <v>2.1585821284854537e-39</v>
+      </c>
+      <c r="T19" s="0">
         <v>-4.5181540160988174</v>
       </c>
-      <c r="Q19" s="0">
+      <c r="U19" s="0">
         <v>6.8362632375642074e-06</v>
       </c>
-      <c r="R19" s="0">
+      <c r="V19" s="0">
         <v>1.118932599995754</v>
       </c>
-      <c r="S19" s="0">
+      <c r="W19" s="0">
         <v>0.26435152600977274</v>
       </c>
-      <c r="T19" s="0">
+      <c r="X19" s="0">
         <v>12.925211523342714</v>
       </c>
-      <c r="U19" s="0">
+      <c r="Y19" s="0">
         <v>1.1041147034956196e-34</v>
       </c>
-      <c r="V19" s="0">
+      <c r="Z19" s="0">
         <v>-4.9036187631235943</v>
       </c>
-      <c r="W19" s="0">
+      <c r="AA19" s="0">
         <v>1.7105579195652288e-06</v>
       </c>
-      <c r="X19" s="0">
+      <c r="AB19" s="0">
+        <v>9.2263444138904571</v>
+      </c>
+      <c r="AC19" s="0">
+        <v>1.6562519343523402e-19</v>
+      </c>
+      <c r="AD19" s="0">
         <v>-4.6686257515628817</v>
       </c>
-      <c r="Y19" s="0">
+      <c r="AE19" s="0">
         <v>3.3636488309913417e-06</v>
       </c>
     </row>
@@ -10604,66 +10956,84 @@
         <v>1.7973114295741928</v>
       </c>
       <c r="E20" s="0">
+        <v>0.96277974739517913</v>
+      </c>
+      <c r="F20" s="0">
         <v>1.6727315026393457</v>
       </c>
-      <c r="F20" s="0">
+      <c r="G20" s="0">
         <v>0.86590099813552146</v>
       </c>
-      <c r="G20" s="0">
+      <c r="H20" s="0">
         <v>0.72196655089809325</v>
       </c>
-      <c r="H20" s="0">
+      <c r="I20" s="0">
         <v>1.6349862017184988</v>
       </c>
-      <c r="I20" s="0">
+      <c r="J20" s="0">
+        <v>0.76599971806980394</v>
+      </c>
+      <c r="K20" s="0">
         <v>1.2739151146970735</v>
       </c>
-      <c r="J20" s="0">
+      <c r="L20" s="0">
         <v>2.9854206678372823</v>
       </c>
-      <c r="K20" s="0">
+      <c r="M20" s="0">
         <v>0.0031421337876795718</v>
       </c>
-      <c r="L20" s="0">
+      <c r="N20" s="0">
         <v>14.271340635821616</v>
       </c>
-      <c r="M20" s="0">
+      <c r="O20" s="0">
         <v>4.1563871914093921e-41</v>
       </c>
-      <c r="N20" s="0">
+      <c r="P20" s="0">
         <v>-4.2103899342919568</v>
       </c>
-      <c r="O20" s="0">
+      <c r="Q20" s="0">
         <v>3.5777279852339422e-05</v>
       </c>
-      <c r="P20" s="0">
+      <c r="R20" s="0">
+        <v>11.425411036545187</v>
+      </c>
+      <c r="S20" s="0">
+        <v>1.759361970823571e-28</v>
+      </c>
+      <c r="T20" s="0">
         <v>-3.9984727105108422</v>
       </c>
-      <c r="Q20" s="0">
+      <c r="U20" s="0">
         <v>6.7535508980656921e-05</v>
       </c>
-      <c r="R20" s="0">
+      <c r="V20" s="0">
         <v>1.225318965398668</v>
       </c>
-      <c r="S20" s="0">
+      <c r="W20" s="0">
         <v>0.22172489860480538</v>
       </c>
-      <c r="T20" s="0">
+      <c r="X20" s="0">
         <v>10.746340004016888</v>
       </c>
-      <c r="U20" s="0">
+      <c r="Y20" s="0">
         <v>3.5856802368051489e-25</v>
       </c>
-      <c r="V20" s="0">
+      <c r="Z20" s="0">
         <v>-4.3023358355090346</v>
       </c>
-      <c r="W20" s="0">
+      <c r="AA20" s="0">
         <v>2.4399952451582194e-05</v>
       </c>
-      <c r="X20" s="0">
+      <c r="AB20" s="0">
+        <v>7.2734980837095211</v>
+      </c>
+      <c r="AC20" s="0">
+        <v>7.1281873421890072e-13</v>
+      </c>
+      <c r="AD20" s="0">
         <v>-4.138311737385628</v>
       </c>
-      <c r="Y20" s="0">
+      <c r="AE20" s="0">
         <v>3.7360249597983091e-05</v>
       </c>
     </row>
@@ -10681,66 +11051,84 @@
         <v>1.6531244091783948</v>
       </c>
       <c r="E21" s="0">
+        <v>0.98995203609796179</v>
+      </c>
+      <c r="F21" s="0">
         <v>1.5399021292774326</v>
       </c>
-      <c r="F21" s="0">
+      <c r="G21" s="0">
         <v>0.940732951819644</v>
       </c>
-      <c r="G21" s="0">
+      <c r="H21" s="0">
         <v>0.67530029026900795</v>
       </c>
-      <c r="H21" s="0">
+      <c r="I21" s="0">
         <v>1.4458640831591036</v>
       </c>
-      <c r="I21" s="0">
+      <c r="J21" s="0">
+        <v>0.75650281671920172</v>
+      </c>
+      <c r="K21" s="0">
         <v>1.1594287628088877</v>
       </c>
-      <c r="J21" s="0">
+      <c r="L21" s="0">
         <v>2.0732755705289176</v>
       </c>
-      <c r="K21" s="0">
+      <c r="M21" s="0">
         <v>0.039275165937858764</v>
       </c>
-      <c r="L21" s="0">
+      <c r="N21" s="0">
         <v>14.198451510843599</v>
       </c>
-      <c r="M21" s="0">
+      <c r="O21" s="0">
         <v>9.4647405506219975e-41</v>
       </c>
-      <c r="N21" s="0">
+      <c r="P21" s="0">
         <v>-4.5542183301429109</v>
       </c>
-      <c r="O21" s="0">
+      <c r="Q21" s="0">
         <v>8.2777415241434567e-06</v>
       </c>
-      <c r="P21" s="0">
+      <c r="R21" s="0">
+        <v>10.15867512831324</v>
+      </c>
+      <c r="S21" s="0">
+        <v>3.9715476433477314e-23</v>
+      </c>
+      <c r="T21" s="0">
         <v>-4.2698890167914216</v>
       </c>
-      <c r="Q21" s="0">
+      <c r="U21" s="0">
         <v>2.1056620457540116e-05</v>
       </c>
-      <c r="R21" s="0">
+      <c r="V21" s="0">
         <v>0.51162463182345819</v>
       </c>
-      <c r="S21" s="0">
+      <c r="W21" s="0">
         <v>0.60941106956971414</v>
       </c>
-      <c r="T21" s="0">
+      <c r="X21" s="0">
         <v>12.275823767332977</v>
       </c>
-      <c r="U21" s="0">
+      <c r="Y21" s="0">
         <v>9.9973813919239814e-32</v>
       </c>
-      <c r="V21" s="0">
+      <c r="Z21" s="0">
         <v>-4.363128311731205</v>
       </c>
-      <c r="W21" s="0">
+      <c r="AA21" s="0">
         <v>1.8878430392656289e-05</v>
       </c>
-      <c r="X21" s="0">
+      <c r="AB21" s="0">
+        <v>7.2156059549603029</v>
+      </c>
+      <c r="AC21" s="0">
+        <v>1.0693036604717931e-12</v>
+      </c>
+      <c r="AD21" s="0">
         <v>-4.1668086857186992</v>
       </c>
-      <c r="Y21" s="0">
+      <c r="AE21" s="0">
         <v>3.3041514305593289e-05</v>
       </c>
     </row>
@@ -10780,61 +11168,61 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="I1" s="0" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="J1" s="0" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="K1" s="0" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="L1" s="0" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="M1" s="0" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="N1" s="0" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="O1" s="0" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="P1" s="0" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="Q1" s="0" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="R1" s="0" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="S1" s="0" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="T1" s="0" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
     </row>
     <row r="2">
@@ -12051,61 +12439,61 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="I1" s="0" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="J1" s="0" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="K1" s="0" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="L1" s="0" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="M1" s="0" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="N1" s="0" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="O1" s="0" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="P1" s="0" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="Q1" s="0" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="R1" s="0" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="S1" s="0" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="T1" s="0" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
     </row>
     <row r="2">
@@ -13322,61 +13710,61 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="I1" s="0" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="J1" s="0" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="K1" s="0" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="L1" s="0" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="M1" s="0" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="N1" s="0" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="O1" s="0" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="P1" s="0" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="Q1" s="0" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="R1" s="0" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="S1" s="0" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="T1" s="0" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
     </row>
     <row r="2">
@@ -14593,61 +14981,61 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="I1" s="0" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="J1" s="0" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="K1" s="0" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="L1" s="0" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="M1" s="0" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="N1" s="0" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="O1" s="0" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="P1" s="0" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="Q1" s="0" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="R1" s="0" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="S1" s="0" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="T1" s="0" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
     </row>
     <row r="2">
@@ -15864,61 +16252,61 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="I1" s="0" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="J1" s="0" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="K1" s="0" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="L1" s="0" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="M1" s="0" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="N1" s="0" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="O1" s="0" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="P1" s="0" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="Q1" s="0" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="R1" s="0" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="S1" s="0" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="T1" s="0" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
     </row>
     <row r="2">
@@ -17135,61 +17523,61 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="I1" s="0" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="J1" s="0" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="K1" s="0" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="L1" s="0" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="M1" s="0" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="N1" s="0" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="O1" s="0" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="P1" s="0" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="Q1" s="0" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="R1" s="0" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="S1" s="0" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="T1" s="0" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
     </row>
     <row r="2">
@@ -18406,61 +18794,61 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="I1" s="0" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="J1" s="0" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="K1" s="0" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="L1" s="0" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="M1" s="0" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="N1" s="0" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="O1" s="0" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="P1" s="0" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="Q1" s="0" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="R1" s="0" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="S1" s="0" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="T1" s="0" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
     </row>
     <row r="2">
@@ -19677,61 +20065,61 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="I1" s="0" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="J1" s="0" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="K1" s="0" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="L1" s="0" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="M1" s="0" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="N1" s="0" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="O1" s="0" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="P1" s="0" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="Q1" s="0" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="R1" s="0" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="S1" s="0" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="T1" s="0" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
     </row>
     <row r="2">
@@ -20910,61 +21298,61 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="I1" s="0" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="J1" s="0" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="K1" s="0" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="L1" s="0" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="M1" s="0" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="N1" s="0" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="O1" s="0" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="P1" s="0" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="Q1" s="0" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="R1" s="0" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="S1" s="0" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="T1" s="0" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
     </row>
     <row r="2">
@@ -22143,61 +22531,61 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="I1" s="0" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="J1" s="0" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="K1" s="0" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="L1" s="0" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="M1" s="0" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="N1" s="0" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="O1" s="0" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="P1" s="0" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="Q1" s="0" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="R1" s="0" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="S1" s="0" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="T1" s="0" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
     </row>
     <row r="2">
@@ -23384,7 +23772,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Y21"/>
+  <dimension ref="A1:AE21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="22.85546875" customWidth="true"/>
@@ -23393,25 +23781,31 @@
     <col min="4" max="4" width="13" customWidth="true"/>
     <col min="5" max="5" width="12.7109375" customWidth="true"/>
     <col min="6" max="6" width="12.7109375" customWidth="true"/>
-    <col min="7" max="7" width="13.85546875" customWidth="true"/>
-    <col min="8" max="8" width="12.7109375" customWidth="true"/>
+    <col min="7" max="7" width="12.7109375" customWidth="true"/>
+    <col min="8" max="8" width="13.85546875" customWidth="true"/>
     <col min="9" max="9" width="12.7109375" customWidth="true"/>
-    <col min="10" max="10" width="13.7109375" customWidth="true"/>
-    <col min="11" max="11" width="16.85546875" customWidth="true"/>
-    <col min="12" max="12" width="17.5703125" customWidth="true"/>
-    <col min="13" max="13" width="20.7109375" customWidth="true"/>
-    <col min="14" max="14" width="15.28515625" customWidth="true"/>
-    <col min="15" max="15" width="18.42578125" customWidth="true"/>
-    <col min="16" max="16" width="13.5703125" customWidth="true"/>
-    <col min="17" max="17" width="16.7109375" customWidth="true"/>
-    <col min="18" max="18" width="19.140625" customWidth="true"/>
-    <col min="19" max="19" width="22.28515625" customWidth="true"/>
-    <col min="20" max="20" width="23" customWidth="true"/>
-    <col min="21" max="21" width="26.140625" customWidth="true"/>
-    <col min="22" max="22" width="20.7109375" customWidth="true"/>
-    <col min="23" max="23" width="23.85546875" customWidth="true"/>
-    <col min="24" max="24" width="19" customWidth="true"/>
-    <col min="25" max="25" width="22.140625" customWidth="true"/>
+    <col min="10" max="10" width="12.7109375" customWidth="true"/>
+    <col min="11" max="11" width="12.7109375" customWidth="true"/>
+    <col min="12" max="12" width="13.7109375" customWidth="true"/>
+    <col min="13" max="13" width="16.85546875" customWidth="true"/>
+    <col min="14" max="14" width="17.5703125" customWidth="true"/>
+    <col min="15" max="15" width="20.7109375" customWidth="true"/>
+    <col min="16" max="16" width="15.28515625" customWidth="true"/>
+    <col min="17" max="17" width="18.42578125" customWidth="true"/>
+    <col min="18" max="18" width="15.42578125" customWidth="true"/>
+    <col min="19" max="19" width="16.42578125" customWidth="true"/>
+    <col min="20" max="20" width="13.5703125" customWidth="true"/>
+    <col min="21" max="21" width="16.7109375" customWidth="true"/>
+    <col min="22" max="22" width="19.140625" customWidth="true"/>
+    <col min="23" max="23" width="22.28515625" customWidth="true"/>
+    <col min="24" max="24" width="23" customWidth="true"/>
+    <col min="25" max="25" width="26.140625" customWidth="true"/>
+    <col min="26" max="26" width="20.7109375" customWidth="true"/>
+    <col min="27" max="27" width="23.85546875" customWidth="true"/>
+    <col min="28" max="28" width="18.7109375" customWidth="true"/>
+    <col min="29" max="29" width="21.85546875" customWidth="true"/>
+    <col min="30" max="30" width="19" customWidth="true"/>
+    <col min="31" max="31" width="22.140625" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -23490,6 +23884,24 @@
       <c r="Y1" s="0" t="s">
         <v>44</v>
       </c>
+      <c r="Z1" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA1" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB1" s="0" t="s">
+        <v>47</v>
+      </c>
+      <c r="AC1" s="0" t="s">
+        <v>48</v>
+      </c>
+      <c r="AD1" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="AE1" s="0" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
@@ -23505,66 +23917,84 @@
         <v>0.60491515003217544</v>
       </c>
       <c r="E2" s="0">
+        <v>1.010149950235613</v>
+      </c>
+      <c r="F2" s="0">
         <v>0.64939191977689481</v>
       </c>
-      <c r="F2" s="0">
+      <c r="G2" s="0">
         <v>1.0630009271661174</v>
       </c>
-      <c r="G2" s="0">
+      <c r="H2" s="0">
         <v>1.4808227012632365</v>
       </c>
-      <c r="H2" s="0">
+      <c r="I2" s="0">
         <v>0.69162794182913501</v>
       </c>
-      <c r="I2" s="0">
+      <c r="J2" s="0">
+        <v>1.3218721436316601</v>
+      </c>
+      <c r="K2" s="0">
         <v>0.8624936969627629</v>
       </c>
-      <c r="J2" s="0">
+      <c r="L2" s="0">
         <v>-2.0732755705289176</v>
       </c>
-      <c r="K2" s="0">
+      <c r="M2" s="0">
         <v>0.039275165937858764</v>
       </c>
-      <c r="L2" s="0">
+      <c r="N2" s="0">
         <v>-14.198451510843599</v>
       </c>
-      <c r="M2" s="0">
+      <c r="O2" s="0">
         <v>9.4647405506219975e-41</v>
       </c>
-      <c r="N2" s="0">
+      <c r="P2" s="0">
         <v>4.5542183301429109</v>
       </c>
-      <c r="O2" s="0">
+      <c r="Q2" s="0">
         <v>8.2777415241434567e-06</v>
       </c>
-      <c r="P2" s="0">
+      <c r="R2" s="0">
+        <v>-10.15867512831324</v>
+      </c>
+      <c r="S2" s="0">
+        <v>3.9715476433477314e-23</v>
+      </c>
+      <c r="T2" s="0">
         <v>4.2698890167914216</v>
       </c>
-      <c r="Q2" s="0">
+      <c r="U2" s="0">
         <v>2.1056620457540116e-05</v>
       </c>
-      <c r="R2" s="0">
+      <c r="V2" s="0">
         <v>-0.51162463182345819</v>
       </c>
-      <c r="S2" s="0">
+      <c r="W2" s="0">
         <v>0.60941106956971414</v>
       </c>
-      <c r="T2" s="0">
+      <c r="X2" s="0">
         <v>-12.275823767332977</v>
       </c>
-      <c r="U2" s="0">
+      <c r="Y2" s="0">
         <v>9.9973813919239814e-32</v>
       </c>
-      <c r="V2" s="0">
+      <c r="Z2" s="0">
         <v>4.363128311731205</v>
       </c>
-      <c r="W2" s="0">
+      <c r="AA2" s="0">
         <v>1.8878430392656289e-05</v>
       </c>
-      <c r="X2" s="0">
+      <c r="AB2" s="0">
+        <v>-7.2156059549603029</v>
+      </c>
+      <c r="AC2" s="0">
+        <v>1.0693036604717931e-12</v>
+      </c>
+      <c r="AD2" s="0">
         <v>4.1668086857186992</v>
       </c>
-      <c r="Y2" s="0">
+      <c r="AE2" s="0">
         <v>3.3041514305593289e-05</v>
       </c>
     </row>
@@ -23582,66 +24012,84 @@
         <v>0.76043637648146489</v>
       </c>
       <c r="E3" s="0">
+        <v>0.9206890270817476</v>
+      </c>
+      <c r="F3" s="0">
         <v>0.77068783045245171</v>
       </c>
-      <c r="F3" s="0">
+      <c r="G3" s="0">
         <v>0.92318270230738353</v>
       </c>
-      <c r="G3" s="0">
+      <c r="H3" s="0">
         <v>0.86704237299434461</v>
       </c>
-      <c r="H3" s="0">
+      <c r="I3" s="0">
         <v>0.76698416851476847</v>
       </c>
-      <c r="I3" s="0">
+      <c r="J3" s="0">
+        <v>0.88839965306719648</v>
+      </c>
+      <c r="K3" s="0">
         <v>0.79990116861351146</v>
       </c>
-      <c r="J3" s="0">
+      <c r="L3" s="0">
         <v>-0.73366070511723402</v>
       </c>
-      <c r="K3" s="0">
+      <c r="M3" s="0">
         <v>0.46391259634308601</v>
       </c>
-      <c r="L3" s="0">
+      <c r="N3" s="0">
         <v>4.7039242796072811</v>
       </c>
-      <c r="M3" s="0">
+      <c r="O3" s="0">
         <v>3.0320324396598226e-06</v>
       </c>
-      <c r="N3" s="0">
+      <c r="P3" s="0">
         <v>2.4472459514010372</v>
       </c>
-      <c r="O3" s="0">
+      <c r="Q3" s="0">
         <v>0.015095555786140753</v>
       </c>
-      <c r="P3" s="0">
+      <c r="R3" s="0">
+        <v>2.5367374782326677</v>
+      </c>
+      <c r="S3" s="0">
+        <v>0.011342168953795992</v>
+      </c>
+      <c r="T3" s="0">
         <v>2.4504449687265857</v>
       </c>
-      <c r="Q3" s="0">
+      <c r="U3" s="0">
         <v>0.014406034129505139</v>
       </c>
-      <c r="R3" s="0">
+      <c r="V3" s="0">
         <v>0.23602107082205734</v>
       </c>
-      <c r="S3" s="0">
+      <c r="W3" s="0">
         <v>0.81362913428527217</v>
       </c>
-      <c r="T3" s="0">
+      <c r="X3" s="0">
         <v>4.2901673118416035</v>
       </c>
-      <c r="U3" s="0">
+      <c r="Y3" s="0">
         <v>2.0161653278175969e-05</v>
       </c>
-      <c r="V3" s="0">
+      <c r="Z3" s="0">
         <v>2.0689399843764562</v>
       </c>
-      <c r="W3" s="0">
+      <c r="AA3" s="0">
         <v>0.039596443684354665</v>
       </c>
-      <c r="X3" s="0">
+      <c r="AB3" s="0">
+        <v>2.7332291397745299</v>
+      </c>
+      <c r="AC3" s="0">
+        <v>0.0063837955100704748</v>
+      </c>
+      <c r="AD3" s="0">
         <v>2.0758839033387271</v>
       </c>
-      <c r="Y3" s="0">
+      <c r="AE3" s="0">
         <v>0.038111365310550781</v>
       </c>
     </row>
@@ -23659,66 +24107,84 @@
         <v>0.67100627616481889</v>
       </c>
       <c r="E4" s="0">
+        <v>0.89103097155083133</v>
+      </c>
+      <c r="F4" s="0">
         <v>0.68811113837944737</v>
       </c>
-      <c r="F4" s="0">
+      <c r="G4" s="0">
         <v>0.90284284744358823</v>
       </c>
-      <c r="G4" s="0">
+      <c r="H4" s="0">
         <v>0.92637415776244103</v>
       </c>
-      <c r="H4" s="0">
+      <c r="I4" s="0">
         <v>0.7608382684058238</v>
       </c>
-      <c r="I4" s="0">
+      <c r="J4" s="0">
+        <v>0.91742221909178245</v>
+      </c>
+      <c r="K4" s="0">
         <v>0.80328980528508909</v>
       </c>
-      <c r="J4" s="0">
+      <c r="L4" s="0">
         <v>1.5476545359896576</v>
       </c>
-      <c r="K4" s="0">
+      <c r="M4" s="0">
         <v>0.12309849225222858</v>
       </c>
-      <c r="L4" s="0">
+      <c r="N4" s="0">
         <v>3.8227830366919782</v>
       </c>
-      <c r="M4" s="0">
+      <c r="O4" s="0">
         <v>0.00014276932787672984</v>
       </c>
-      <c r="N4" s="0">
+      <c r="P4" s="0">
         <v>3.6595757226895205</v>
       </c>
-      <c r="O4" s="0">
+      <c r="Q4" s="0">
         <v>0.00030912199125550155</v>
       </c>
-      <c r="P4" s="0">
+      <c r="R4" s="0">
+        <v>3.6147737520600058</v>
+      </c>
+      <c r="S4" s="0">
+        <v>0.00031579829651332615</v>
+      </c>
+      <c r="T4" s="0">
         <v>3.6222966541620654</v>
       </c>
-      <c r="Q4" s="0">
+      <c r="U4" s="0">
         <v>0.00030385438794241305</v>
       </c>
-      <c r="R4" s="0">
+      <c r="V4" s="0">
         <v>1.5413490897303512</v>
       </c>
-      <c r="S4" s="0">
+      <c r="W4" s="0">
         <v>0.12462468622783252</v>
       </c>
-      <c r="T4" s="0">
+      <c r="X4" s="0">
         <v>2.3306766843795028</v>
       </c>
-      <c r="U4" s="0">
+      <c r="Y4" s="0">
         <v>0.020031519721894112</v>
       </c>
-      <c r="V4" s="0">
+      <c r="Z4" s="0">
         <v>3.2038732188769896</v>
       </c>
-      <c r="W4" s="0">
+      <c r="AA4" s="0">
         <v>0.0015350416489228736</v>
       </c>
-      <c r="X4" s="0">
+      <c r="AB4" s="0">
+        <v>2.5964923580157682</v>
+      </c>
+      <c r="AC4" s="0">
+        <v>0.0095581120073967036</v>
+      </c>
+      <c r="AD4" s="0">
         <v>3.1768102303688148</v>
       </c>
-      <c r="Y4" s="0">
+      <c r="AE4" s="0">
         <v>0.001525954725893096</v>
       </c>
     </row>
@@ -23736,66 +24202,84 @@
         <v>0.65103222849210984</v>
       </c>
       <c r="E5" s="0">
+        <v>1.0110477930911965</v>
+      </c>
+      <c r="F5" s="0">
         <v>0.68862267226368268</v>
       </c>
-      <c r="F5" s="0">
+      <c r="G5" s="0">
         <v>1.1557920202937191</v>
       </c>
-      <c r="G5" s="0">
+      <c r="H5" s="0">
         <v>1.1547665426410001</v>
       </c>
-      <c r="H5" s="0">
+      <c r="I5" s="0">
         <v>0.9199888507657229</v>
       </c>
-      <c r="I5" s="0">
+      <c r="J5" s="0">
+        <v>1.1551566617177063</v>
+      </c>
+      <c r="K5" s="0">
         <v>0.98374528912169712</v>
       </c>
-      <c r="J5" s="0">
+      <c r="L5" s="0">
         <v>-5.2990080289634314</v>
       </c>
-      <c r="K5" s="0">
+      <c r="M5" s="0">
         <v>2.75217309179785e-07</v>
       </c>
-      <c r="L5" s="0">
+      <c r="N5" s="0">
         <v>5.806062513195184</v>
       </c>
-      <c r="M5" s="0">
+      <c r="O5" s="0">
         <v>9.3998986068638692e-09</v>
       </c>
-      <c r="N5" s="0">
+      <c r="P5" s="0">
         <v>3.3792556075944011</v>
       </c>
-      <c r="O5" s="0">
+      <c r="Q5" s="0">
         <v>0.00084500826710995683</v>
       </c>
-      <c r="P5" s="0">
+      <c r="R5" s="0">
+        <v>-0.74459417188256161</v>
+      </c>
+      <c r="S5" s="0">
+        <v>0.45669433674637527</v>
+      </c>
+      <c r="T5" s="0">
         <v>3.3225838803351539</v>
       </c>
-      <c r="Q5" s="0">
+      <c r="U5" s="0">
         <v>0.00091801428876398937</v>
       </c>
-      <c r="R5" s="0">
+      <c r="V5" s="0">
         <v>-5.2437979750349983</v>
       </c>
-      <c r="S5" s="0">
+      <c r="W5" s="0">
         <v>3.5979842524191974e-07</v>
       </c>
-      <c r="T5" s="0">
+      <c r="X5" s="0">
         <v>-1.5409290759951946</v>
       </c>
-      <c r="U5" s="0">
+      <c r="Y5" s="0">
         <v>0.12375083834470424</v>
       </c>
-      <c r="V5" s="0">
+      <c r="Z5" s="0">
         <v>2.5727303038619045</v>
       </c>
-      <c r="W5" s="0">
+      <c r="AA5" s="0">
         <v>0.010677427785223488</v>
       </c>
-      <c r="X5" s="0">
+      <c r="AB5" s="0">
+        <v>-5.0956633250060293</v>
+      </c>
+      <c r="AC5" s="0">
+        <v>4.1632152876522253e-07</v>
+      </c>
+      <c r="AD5" s="0">
         <v>2.5234195727596225</v>
       </c>
-      <c r="Y5" s="0">
+      <c r="AE5" s="0">
         <v>0.011746723040088572</v>
       </c>
     </row>
@@ -23813,66 +24297,84 @@
         <v>0.81835187823886824</v>
       </c>
       <c r="E6" s="0">
+        <v>1.0952436766260023</v>
+      </c>
+      <c r="F6" s="0">
         <v>0.82639244116851485</v>
       </c>
-      <c r="F6" s="0">
+      <c r="G6" s="0">
         <v>1.0745090698776689</v>
       </c>
-      <c r="G6" s="0">
+      <c r="H6" s="0">
         <v>0.80344592748665145</v>
       </c>
-      <c r="H6" s="0">
+      <c r="I6" s="0">
         <v>0.80468554931919645</v>
       </c>
-      <c r="I6" s="0">
+      <c r="J6" s="0">
+        <v>0.90656558353982064</v>
+      </c>
+      <c r="K6" s="0">
         <v>0.83230628574225241</v>
       </c>
-      <c r="J6" s="0">
+      <c r="L6" s="0">
         <v>-6.3778363028744476</v>
       </c>
-      <c r="K6" s="0">
+      <c r="M6" s="0">
         <v>9.9469109357882391e-10</v>
       </c>
-      <c r="L6" s="0">
+      <c r="N6" s="0">
         <v>4.2191646619639274</v>
       </c>
-      <c r="M6" s="0">
+      <c r="O6" s="0">
         <v>2.7485690460634162e-05</v>
       </c>
-      <c r="N6" s="0">
+      <c r="P6" s="0">
         <v>1.9956390465562508</v>
       </c>
-      <c r="O6" s="0">
+      <c r="Q6" s="0">
         <v>0.047075991311462388</v>
       </c>
-      <c r="P6" s="0">
+      <c r="R6" s="0">
+        <v>-3.3780774905824891</v>
+      </c>
+      <c r="S6" s="0">
+        <v>0.0007584702408800735</v>
+      </c>
+      <c r="T6" s="0">
         <v>1.9541926215735201</v>
       </c>
-      <c r="Q6" s="0">
+      <c r="U6" s="0">
         <v>0.050904047593779693</v>
       </c>
-      <c r="R6" s="0">
+      <c r="V6" s="0">
         <v>-5.3473414670690707</v>
       </c>
-      <c r="S6" s="0">
+      <c r="W6" s="0">
         <v>2.1730485732681933e-07</v>
       </c>
-      <c r="T6" s="0">
+      <c r="X6" s="0">
         <v>4.8503869316990551</v>
       </c>
-      <c r="U6" s="0">
+      <c r="Y6" s="0">
         <v>1.4954865892715061e-06</v>
       </c>
-      <c r="V6" s="0">
+      <c r="Z6" s="0">
         <v>1.592963156236594</v>
       </c>
-      <c r="W6" s="0">
+      <c r="AA6" s="0">
         <v>0.11245252027466746</v>
       </c>
-      <c r="X6" s="0">
+      <c r="AB6" s="0">
+        <v>-3.0732786280899402</v>
+      </c>
+      <c r="AC6" s="0">
+        <v>0.002175330425611955</v>
+      </c>
+      <c r="AD6" s="0">
         <v>1.5658328667945003</v>
       </c>
-      <c r="Y6" s="0">
+      <c r="AE6" s="0">
         <v>0.11764413635318838</v>
       </c>
     </row>
@@ -23890,66 +24392,84 @@
         <v>0.64863223269128412</v>
       </c>
       <c r="E7" s="0">
+        <v>1.0328490386665359</v>
+      </c>
+      <c r="F7" s="0">
         <v>0.67247600667803487</v>
       </c>
-      <c r="F7" s="0">
+      <c r="G7" s="0">
         <v>0.96666435016385832</v>
       </c>
-      <c r="G7" s="0">
+      <c r="H7" s="0">
         <v>0.91406787249787314</v>
       </c>
-      <c r="H7" s="0">
+      <c r="I7" s="0">
         <v>0.7086401086359998</v>
       </c>
-      <c r="I7" s="0">
+      <c r="J7" s="0">
+        <v>0.93407697679247614</v>
+      </c>
+      <c r="K7" s="0">
         <v>0.76975838723713419</v>
       </c>
-      <c r="J7" s="0">
+      <c r="L7" s="0">
         <v>-3.1238713543929388</v>
       </c>
-      <c r="K7" s="0">
+      <c r="M7" s="0">
         <v>0.0020173401833881522</v>
       </c>
-      <c r="L7" s="0">
+      <c r="N7" s="0">
         <v>0.44529954792840065</v>
       </c>
-      <c r="M7" s="0">
+      <c r="O7" s="0">
         <v>0.65623026714334742</v>
       </c>
-      <c r="N7" s="0">
+      <c r="P7" s="0">
         <v>4.2719246245586611</v>
       </c>
-      <c r="O7" s="0">
+      <c r="Q7" s="0">
         <v>2.7712373977843202e-05</v>
       </c>
-      <c r="P7" s="0">
+      <c r="R7" s="0">
+        <v>-2.0614266524956522</v>
+      </c>
+      <c r="S7" s="0">
+        <v>0.039523787734903885</v>
+      </c>
+      <c r="T7" s="0">
         <v>4.1469664326372486</v>
       </c>
-      <c r="Q7" s="0">
+      <c r="U7" s="0">
         <v>3.5994918583317133e-05</v>
       </c>
-      <c r="R7" s="0">
+      <c r="V7" s="0">
         <v>-2.3580996159726793</v>
       </c>
-      <c r="S7" s="0">
+      <c r="W7" s="0">
         <v>0.019218143203938422</v>
       </c>
-      <c r="T7" s="0">
+      <c r="X7" s="0">
         <v>0.72054017222790689</v>
       </c>
-      <c r="U7" s="0">
+      <c r="Y7" s="0">
         <v>0.471414323171089</v>
       </c>
-      <c r="V7" s="0">
+      <c r="Z7" s="0">
         <v>3.9432688993138956</v>
       </c>
-      <c r="W7" s="0">
+      <c r="AA7" s="0">
         <v>0.00010485254004311664</v>
       </c>
-      <c r="X7" s="0">
+      <c r="AB7" s="0">
+        <v>-1.5565900645204598</v>
+      </c>
+      <c r="AC7" s="0">
+        <v>0.11988841662527305</v>
+      </c>
+      <c r="AD7" s="0">
         <v>3.8498523686692945</v>
       </c>
-      <c r="Y7" s="0">
+      <c r="AE7" s="0">
         <v>0.00012424759217757072</v>
       </c>
     </row>
@@ -23967,66 +24487,84 @@
         <v>0.76050657513057018</v>
       </c>
       <c r="E8" s="0">
+        <v>1.1632769539367196</v>
+      </c>
+      <c r="F8" s="0">
         <v>0.80729426169499585</v>
       </c>
-      <c r="F8" s="0">
+      <c r="G8" s="0">
         <v>1.2453636984170944</v>
       </c>
-      <c r="G8" s="0">
+      <c r="H8" s="0">
         <v>0.92674730167375363</v>
       </c>
-      <c r="H8" s="0">
+      <c r="I8" s="0">
         <v>0.91715932097528274</v>
       </c>
-      <c r="I8" s="0">
+      <c r="J8" s="0">
+        <v>1.047957485231938</v>
+      </c>
+      <c r="K8" s="0">
         <v>0.95262006308427283</v>
       </c>
-      <c r="J8" s="0">
+      <c r="L8" s="0">
         <v>-6.7479897858478433</v>
       </c>
-      <c r="K8" s="0">
+      <c r="M8" s="0">
         <v>1.2343358531882273e-10</v>
       </c>
-      <c r="L8" s="0">
+      <c r="N8" s="0">
         <v>7.7988158274453623</v>
       </c>
-      <c r="M8" s="0">
+      <c r="O8" s="0">
         <v>2.0650376228004544e-14</v>
       </c>
-      <c r="N8" s="0">
+      <c r="P8" s="0">
         <v>2.9371959603028102</v>
       </c>
-      <c r="O8" s="0">
+      <c r="Q8" s="0">
         <v>0.0036261809775820202</v>
       </c>
-      <c r="P8" s="0">
+      <c r="R8" s="0">
+        <v>-3.9535345071440253</v>
+      </c>
+      <c r="S8" s="0">
+        <v>8.250008613299524e-05</v>
+      </c>
+      <c r="T8" s="0">
         <v>2.8346657787053635</v>
       </c>
-      <c r="Q8" s="0">
+      <c r="U8" s="0">
         <v>0.0046621610327883941</v>
       </c>
-      <c r="R8" s="0">
+      <c r="V8" s="0">
         <v>-6.8532418639756871</v>
       </c>
-      <c r="S8" s="0">
+      <c r="W8" s="0">
         <v>6.727724513533151e-11</v>
       </c>
-      <c r="T8" s="0">
+      <c r="X8" s="0">
         <v>4.7521309813139494</v>
       </c>
-      <c r="U8" s="0">
+      <c r="Y8" s="0">
         <v>2.4077246951863699e-06</v>
       </c>
-      <c r="V8" s="0">
+      <c r="Z8" s="0">
         <v>2.5202601703378709</v>
       </c>
-      <c r="W8" s="0">
+      <c r="AA8" s="0">
         <v>0.012360652113288597</v>
       </c>
-      <c r="X8" s="0">
+      <c r="AB8" s="0">
+        <v>-5.1694391543770495</v>
+      </c>
+      <c r="AC8" s="0">
+        <v>2.8416905911076153e-07</v>
+      </c>
+      <c r="AD8" s="0">
         <v>2.4231319690859068</v>
       </c>
-      <c r="Y8" s="0">
+      <c r="AE8" s="0">
         <v>0.01553045986734033</v>
       </c>
     </row>
@@ -24044,66 +24582,84 @@
         <v>0.6473188992397465</v>
       </c>
       <c r="E9" s="0">
+        <v>0.96406617839570019</v>
+      </c>
+      <c r="F9" s="0">
         <v>0.66750522759330488</v>
       </c>
-      <c r="F9" s="0">
+      <c r="G9" s="0">
         <v>0.87292341908855897</v>
       </c>
-      <c r="G9" s="0">
+      <c r="H9" s="0">
         <v>1.1289618384928708</v>
       </c>
-      <c r="H9" s="0">
+      <c r="I9" s="0">
         <v>0.74887392636119854</v>
       </c>
-      <c r="I9" s="0">
+      <c r="J9" s="0">
+        <v>1.0315579881852439</v>
+      </c>
+      <c r="K9" s="0">
         <v>0.82551251430800321</v>
       </c>
-      <c r="J9" s="0">
+      <c r="L9" s="0">
         <v>1.49743067244829</v>
       </c>
-      <c r="K9" s="0">
+      <c r="M9" s="0">
         <v>0.13567041747619391</v>
       </c>
-      <c r="L9" s="0">
+      <c r="N9" s="0">
         <v>-2.1584566995685983</v>
       </c>
-      <c r="M9" s="0">
+      <c r="O9" s="0">
         <v>0.031205213195196341</v>
       </c>
-      <c r="N9" s="0">
+      <c r="P9" s="0">
         <v>3.8062572383032101</v>
       </c>
-      <c r="O9" s="0">
+      <c r="Q9" s="0">
         <v>0.00017814790296255577</v>
       </c>
-      <c r="P9" s="0">
+      <c r="R9" s="0">
+        <v>-0.0032487344344871646</v>
+      </c>
+      <c r="S9" s="0">
+        <v>0.99740854599651751</v>
+      </c>
+      <c r="T9" s="0">
         <v>3.731143621223544</v>
       </c>
-      <c r="Q9" s="0">
+      <c r="U9" s="0">
         <v>0.00019927707981346482</v>
       </c>
-      <c r="R9" s="0">
+      <c r="V9" s="0">
         <v>1.2444113587921104</v>
       </c>
-      <c r="S9" s="0">
+      <c r="W9" s="0">
         <v>0.21463152270181085</v>
       </c>
-      <c r="T9" s="0">
+      <c r="X9" s="0">
         <v>-3.1647004663808427</v>
       </c>
-      <c r="U9" s="0">
+      <c r="Y9" s="0">
         <v>0.0016143754098992371</v>
       </c>
-      <c r="V9" s="0">
+      <c r="Z9" s="0">
         <v>3.4931253449180151</v>
       </c>
-      <c r="W9" s="0">
+      <c r="AA9" s="0">
         <v>0.00056591633364870921</v>
       </c>
-      <c r="X9" s="0">
+      <c r="AB9" s="0">
+        <v>-0.53205276229954401</v>
+      </c>
+      <c r="AC9" s="0">
+        <v>0.59480919063597282</v>
+      </c>
+      <c r="AD9" s="0">
         <v>3.4321332681405741</v>
       </c>
-      <c r="Y9" s="0">
+      <c r="AE9" s="0">
         <v>0.00061867656245596502</v>
       </c>
     </row>
@@ -24121,66 +24677,84 @@
         <v>0.70747063587844383</v>
       </c>
       <c r="E10" s="0">
+        <v>0.92637848396819689</v>
+      </c>
+      <c r="F10" s="0">
         <v>0.71753457749022398</v>
       </c>
-      <c r="F10" s="0">
+      <c r="G10" s="0">
         <v>0.94354583443301487</v>
       </c>
-      <c r="G10" s="0">
+      <c r="H10" s="0">
         <v>1.0198466164989892</v>
       </c>
-      <c r="H10" s="0">
+      <c r="I10" s="0">
         <v>0.81893079254621903</v>
       </c>
-      <c r="I10" s="0">
+      <c r="J10" s="0">
+        <v>0.99081976196676746</v>
+      </c>
+      <c r="K10" s="0">
         <v>0.86553167911555795</v>
       </c>
-      <c r="J10" s="0">
+      <c r="L10" s="0">
         <v>1.8792955142613719</v>
       </c>
-      <c r="K10" s="0">
+      <c r="M10" s="0">
         <v>0.061485365822448027</v>
       </c>
-      <c r="L10" s="0">
+      <c r="N10" s="0">
         <v>1.0119028644317454</v>
       </c>
-      <c r="M10" s="0">
+      <c r="O10" s="0">
         <v>0.31190696619144209</v>
       </c>
-      <c r="N10" s="0">
+      <c r="P10" s="0">
         <v>3.4875210171497879</v>
       </c>
-      <c r="O10" s="0">
+      <c r="Q10" s="0">
         <v>0.00057733416747757997</v>
       </c>
-      <c r="P10" s="0">
+      <c r="R10" s="0">
+        <v>2.0873752246468356</v>
+      </c>
+      <c r="S10" s="0">
+        <v>0.037110244287434965</v>
+      </c>
+      <c r="T10" s="0">
         <v>3.4491987994949742</v>
       </c>
-      <c r="Q10" s="0">
+      <c r="U10" s="0">
         <v>0.00058121565696827768</v>
       </c>
-      <c r="R10" s="0">
+      <c r="V10" s="0">
         <v>0.73880300937425647</v>
       </c>
-      <c r="S10" s="0">
+      <c r="W10" s="0">
         <v>0.46078982767548482</v>
       </c>
-      <c r="T10" s="0">
+      <c r="X10" s="0">
         <v>-1.1439254552812901</v>
       </c>
-      <c r="U10" s="0">
+      <c r="Y10" s="0">
         <v>0.25301519324501198</v>
       </c>
-      <c r="V10" s="0">
+      <c r="Z10" s="0">
         <v>3.1399133483658872</v>
       </c>
-      <c r="W10" s="0">
+      <c r="AA10" s="0">
         <v>0.0018965546264604974</v>
       </c>
-      <c r="X10" s="0">
+      <c r="AB10" s="0">
+        <v>-0.10364040267321392</v>
+      </c>
+      <c r="AC10" s="0">
+        <v>0.91747577805652736</v>
+      </c>
+      <c r="AD10" s="0">
         <v>3.0998869385922432</v>
       </c>
-      <c r="Y10" s="0">
+      <c r="AE10" s="0">
         <v>0.0019797652065657667</v>
       </c>
     </row>
@@ -24198,66 +24772,84 @@
         <v>0.76221589505624354</v>
       </c>
       <c r="E11" s="0">
+        <v>0.88581339425509076</v>
+      </c>
+      <c r="F11" s="0">
         <v>0.76647048558114617</v>
       </c>
-      <c r="F11" s="0">
+      <c r="G11" s="0">
         <v>1.4747369747788572</v>
       </c>
-      <c r="G11" s="0">
+      <c r="H11" s="0">
         <v>1.6762072190234572</v>
       </c>
-      <c r="H11" s="0">
+      <c r="I11" s="0">
         <v>0.87260834179242208</v>
       </c>
-      <c r="I11" s="0">
+      <c r="J11" s="0">
+        <v>1.5995625593762912</v>
+      </c>
+      <c r="K11" s="0">
         <v>1.0696931876026541</v>
       </c>
-      <c r="J11" s="0">
+      <c r="L11" s="0">
         <v>0.086853664323501653</v>
       </c>
-      <c r="K11" s="0">
+      <c r="M11" s="0">
         <v>0.93086439509719798</v>
       </c>
-      <c r="L11" s="0">
+      <c r="N11" s="0">
         <v>4.3389874309860774</v>
       </c>
-      <c r="M11" s="0">
+      <c r="O11" s="0">
         <v>1.6250405684605564e-05</v>
       </c>
-      <c r="N11" s="0">
+      <c r="P11" s="0">
         <v>2.3770964987380845</v>
       </c>
-      <c r="O11" s="0">
+      <c r="Q11" s="0">
         <v>0.018215064261376559</v>
       </c>
-      <c r="P11" s="0">
+      <c r="R11" s="0">
+        <v>3.118020527038226</v>
+      </c>
+      <c r="S11" s="0">
+        <v>0.0018734344183433868</v>
+      </c>
+      <c r="T11" s="0">
         <v>2.3869335598789001</v>
       </c>
-      <c r="Q11" s="0">
+      <c r="U11" s="0">
         <v>0.017139452346465061</v>
       </c>
-      <c r="R11" s="0">
+      <c r="V11" s="0">
         <v>-9.2007592579222095</v>
       </c>
-      <c r="S11" s="0">
+      <c r="W11" s="0">
         <v>2.3911289860665512e-17</v>
       </c>
-      <c r="T11" s="0">
+      <c r="X11" s="0">
         <v>-17.899575792520771</v>
       </c>
-      <c r="U11" s="0">
+      <c r="Y11" s="0">
         <v>4.8294960428398118e-60</v>
       </c>
-      <c r="V11" s="0">
+      <c r="Z11" s="0">
         <v>2.7116599864447637</v>
       </c>
-      <c r="W11" s="0">
+      <c r="AA11" s="0">
         <v>0.0071668368541277661</v>
       </c>
-      <c r="X11" s="0">
+      <c r="AB11" s="0">
+        <v>-18.309988215377508</v>
+      </c>
+      <c r="AC11" s="0">
+        <v>1.0658700061149028e-64</v>
+      </c>
+      <c r="AD11" s="0">
         <v>2.5789807495939483</v>
       </c>
-      <c r="Y11" s="0">
+      <c r="AE11" s="0">
         <v>0.010024175347370056</v>
       </c>
     </row>
@@ -24275,66 +24867,84 @@
         <v>0.63262695070531427</v>
       </c>
       <c r="E12" s="0">
+        <v>0.90110458193363629</v>
+      </c>
+      <c r="F12" s="0">
         <v>0.66220549401706152</v>
       </c>
-      <c r="F12" s="0">
+      <c r="G12" s="0">
         <v>2.504899077093913</v>
       </c>
-      <c r="G12" s="0">
+      <c r="H12" s="0">
         <v>3.9676210439506936</v>
       </c>
-      <c r="H12" s="0">
+      <c r="I12" s="0">
         <v>1.2149864842184837</v>
       </c>
-      <c r="I12" s="0">
+      <c r="J12" s="0">
+        <v>3.4111625568499253</v>
+      </c>
+      <c r="K12" s="0">
         <v>1.8103926489770672</v>
       </c>
-      <c r="J12" s="0">
+      <c r="L12" s="0">
         <v>2.3316999399187255</v>
       </c>
-      <c r="K12" s="0">
+      <c r="M12" s="0">
         <v>0.020592671148033651</v>
       </c>
-      <c r="L12" s="0">
+      <c r="N12" s="0">
         <v>2.0963769998824029</v>
       </c>
-      <c r="M12" s="0">
+      <c r="O12" s="0">
         <v>0.036379267848510609</v>
       </c>
-      <c r="N12" s="0">
+      <c r="P12" s="0">
         <v>3.3700808384251824</v>
       </c>
-      <c r="O12" s="0">
+      <c r="Q12" s="0">
         <v>0.00087235210064672171</v>
       </c>
-      <c r="P12" s="0">
+      <c r="R12" s="0">
+        <v>3.1325443704750984</v>
+      </c>
+      <c r="S12" s="0">
+        <v>0.0017840482825383992</v>
+      </c>
+      <c r="T12" s="0">
         <v>3.3445163174932868</v>
       </c>
-      <c r="Q12" s="0">
+      <c r="U12" s="0">
         <v>0.00084901916733002463</v>
       </c>
-      <c r="R12" s="0">
+      <c r="V12" s="0">
         <v>-29.889045109054329</v>
       </c>
-      <c r="S12" s="0">
+      <c r="W12" s="0">
         <v>1.2000546812987231e-80</v>
       </c>
-      <c r="T12" s="0">
+      <c r="X12" s="0">
         <v>-48.938170352807191</v>
       </c>
-      <c r="U12" s="0">
+      <c r="Y12" s="0">
         <v>5.7268661826584746e-237</v>
       </c>
-      <c r="V12" s="0">
+      <c r="Z12" s="0">
         <v>-0.50417700788953579</v>
       </c>
-      <c r="W12" s="0">
+      <c r="AA12" s="0">
         <v>0.61458824889591945</v>
       </c>
-      <c r="X12" s="0">
+      <c r="AB12" s="0">
+        <v>-55.426937358114408</v>
+      </c>
+      <c r="AC12" s="0">
+        <v>2.5007106442099441e-305</v>
+      </c>
+      <c r="AD12" s="0">
         <v>-0.75778921897931251</v>
       </c>
-      <c r="Y12" s="0">
+      <c r="AE12" s="0">
         <v>0.44872186096777045</v>
       </c>
     </row>
@@ -24352,66 +24962,84 @@
         <v>0.74529053115757016</v>
       </c>
       <c r="E13" s="0">
+        <v>0.90157596257746475</v>
+      </c>
+      <c r="F13" s="0">
         <v>0.750979354895565</v>
       </c>
-      <c r="F13" s="0">
+      <c r="G13" s="0">
         <v>1.0075720327757212</v>
       </c>
-      <c r="G13" s="0">
+      <c r="H13" s="0">
         <v>1.0392873414856583</v>
       </c>
-      <c r="H13" s="0">
+      <c r="I13" s="0">
         <v>0.85803856310811155</v>
       </c>
-      <c r="I13" s="0">
+      <c r="J13" s="0">
+        <v>1.0272219913353566</v>
+      </c>
+      <c r="K13" s="0">
         <v>0.90390594933311286</v>
       </c>
-      <c r="J13" s="0">
+      <c r="L13" s="0">
         <v>0.010545343171952727</v>
       </c>
-      <c r="K13" s="0">
+      <c r="M13" s="0">
         <v>0.99159545130366622</v>
       </c>
-      <c r="L13" s="0">
+      <c r="N13" s="0">
         <v>4.1320615618167089</v>
       </c>
-      <c r="M13" s="0">
+      <c r="O13" s="0">
         <v>3.9952913785657567e-05</v>
       </c>
-      <c r="N13" s="0">
+      <c r="P13" s="0">
         <v>2.3278435414423084</v>
       </c>
-      <c r="O13" s="0">
+      <c r="Q13" s="0">
         <v>0.020732121431895602</v>
       </c>
-      <c r="P13" s="0">
+      <c r="R13" s="0">
+        <v>2.8636383238466556</v>
+      </c>
+      <c r="S13" s="0">
+        <v>0.0042767445036604517</v>
+      </c>
+      <c r="T13" s="0">
         <v>2.3362428465675507</v>
       </c>
-      <c r="Q13" s="0">
+      <c r="U13" s="0">
         <v>0.019638011206259041</v>
       </c>
-      <c r="R13" s="0">
+      <c r="V13" s="0">
         <v>-0.30791044860267036</v>
       </c>
-      <c r="S13" s="0">
+      <c r="W13" s="0">
         <v>0.75843281393975581</v>
       </c>
-      <c r="T13" s="0">
+      <c r="X13" s="0">
         <v>-0.32048343816983155</v>
       </c>
-      <c r="U13" s="0">
+      <c r="Y13" s="0">
         <v>0.74869009458790337</v>
       </c>
-      <c r="V13" s="0">
+      <c r="Z13" s="0">
         <v>2.8908812170884883</v>
       </c>
-      <c r="W13" s="0">
+      <c r="AA13" s="0">
         <v>0.0041850412220031941</v>
       </c>
-      <c r="X13" s="0">
+      <c r="AB13" s="0">
+        <v>-0.44289613664821681</v>
+      </c>
+      <c r="AC13" s="0">
+        <v>0.65793791142302793</v>
+      </c>
+      <c r="AD13" s="0">
         <v>2.8589564154264879</v>
       </c>
-      <c r="Y13" s="0">
+      <c r="AE13" s="0">
         <v>0.0043218589255874518</v>
       </c>
     </row>
@@ -24429,66 +25057,84 @@
         <v>0.77700247754099316</v>
       </c>
       <c r="E14" s="0">
+        <v>0.96065072919251449</v>
+      </c>
+      <c r="F14" s="0">
         <v>0.78199320812442874</v>
       </c>
-      <c r="F14" s="0">
+      <c r="G14" s="0">
         <v>1.0267430661386132</v>
       </c>
-      <c r="G14" s="0">
+      <c r="H14" s="0">
         <v>0.94162648092018908</v>
       </c>
-      <c r="H14" s="0">
+      <c r="I14" s="0">
         <v>0.86939940209245115</v>
       </c>
-      <c r="I14" s="0">
+      <c r="J14" s="0">
+        <v>0.97400710233083732</v>
+      </c>
+      <c r="K14" s="0">
         <v>0.89775963712976525</v>
       </c>
-      <c r="J14" s="0">
+      <c r="L14" s="0">
         <v>-3.0592394906961449</v>
       </c>
-      <c r="K14" s="0">
+      <c r="M14" s="0">
         <v>0.002485753013052107</v>
       </c>
-      <c r="L14" s="0">
+      <c r="N14" s="0">
         <v>4.1406270034806214</v>
       </c>
-      <c r="M14" s="0">
+      <c r="O14" s="0">
         <v>3.8521597797832929e-05</v>
       </c>
-      <c r="N14" s="0">
+      <c r="P14" s="0">
         <v>2.0954945469079083</v>
       </c>
-      <c r="O14" s="0">
+      <c r="Q14" s="0">
         <v>0.037149543676132962</v>
       </c>
-      <c r="P14" s="0">
+      <c r="R14" s="0">
+        <v>0.091528533661472344</v>
+      </c>
+      <c r="S14" s="0">
+        <v>0.92709120720346783</v>
+      </c>
+      <c r="T14" s="0">
         <v>2.0881140786741308</v>
       </c>
-      <c r="Q14" s="0">
+      <c r="U14" s="0">
         <v>0.036992161397446502</v>
       </c>
-      <c r="R14" s="0">
+      <c r="V14" s="0">
         <v>-2.1965234690218032</v>
       </c>
-      <c r="S14" s="0">
+      <c r="W14" s="0">
         <v>0.029066476552346305</v>
       </c>
-      <c r="T14" s="0">
+      <c r="X14" s="0">
         <v>1.8958817081216874</v>
       </c>
-      <c r="U14" s="0">
+      <c r="Y14" s="0">
         <v>0.058355275934776636</v>
       </c>
-      <c r="V14" s="0">
+      <c r="Z14" s="0">
         <v>2.7701383479398607</v>
       </c>
-      <c r="W14" s="0">
+      <c r="AA14" s="0">
         <v>0.0060306888200453521</v>
       </c>
-      <c r="X14" s="0">
+      <c r="AB14" s="0">
+        <v>-0.58072670264884463</v>
+      </c>
+      <c r="AC14" s="0">
+        <v>0.56155723040245542</v>
+      </c>
+      <c r="AD14" s="0">
         <v>2.7414262249524626</v>
       </c>
-      <c r="Y14" s="0">
+      <c r="AE14" s="0">
         <v>0.0062056651062558817</v>
       </c>
     </row>
@@ -24506,66 +25152,84 @@
         <v>0.60459072029270211</v>
       </c>
       <c r="E15" s="0">
+        <v>0.87783556342322344</v>
+      </c>
+      <c r="F15" s="0">
         <v>0.62988500481033227</v>
       </c>
-      <c r="F15" s="0">
+      <c r="G15" s="0">
         <v>0.95084681329985099</v>
       </c>
-      <c r="G15" s="0">
+      <c r="H15" s="0">
         <v>1.0233723600584317</v>
       </c>
-      <c r="H15" s="0">
+      <c r="I15" s="0">
         <v>0.91843607591570919</v>
       </c>
-      <c r="I15" s="0">
+      <c r="J15" s="0">
+        <v>0.99578170582620007</v>
+      </c>
+      <c r="K15" s="0">
         <v>0.93940528027037773</v>
       </c>
-      <c r="J15" s="0">
+      <c r="L15" s="0">
         <v>2.0648140764462206</v>
       </c>
-      <c r="K15" s="0">
+      <c r="M15" s="0">
         <v>0.040076691028962622</v>
       </c>
-      <c r="L15" s="0">
+      <c r="N15" s="0">
         <v>3.716317181004984</v>
       </c>
-      <c r="M15" s="0">
+      <c r="O15" s="0">
         <v>0.00021699746965943401</v>
       </c>
-      <c r="N15" s="0">
+      <c r="P15" s="0">
         <v>4.0401644448436036</v>
       </c>
-      <c r="O15" s="0">
+      <c r="Q15" s="0">
         <v>7.1441084071547083e-05</v>
       </c>
-      <c r="P15" s="0">
+      <c r="R15" s="0">
+        <v>3.9138973583456322</v>
+      </c>
+      <c r="S15" s="0">
+        <v>9.7049983175107908e-05</v>
+      </c>
+      <c r="T15" s="0">
         <v>3.9791569040806922</v>
       </c>
-      <c r="Q15" s="0">
+      <c r="U15" s="0">
         <v>7.3187646409169792e-05</v>
       </c>
-      <c r="R15" s="0">
+      <c r="V15" s="0">
         <v>1.0112203293550652</v>
       </c>
-      <c r="S15" s="0">
+      <c r="W15" s="0">
         <v>0.31298763380428185</v>
       </c>
-      <c r="T15" s="0">
+      <c r="X15" s="0">
         <v>-0.079025747146457478</v>
       </c>
-      <c r="U15" s="0">
+      <c r="Y15" s="0">
         <v>0.93703297352132031</v>
       </c>
-      <c r="V15" s="0">
+      <c r="Z15" s="0">
         <v>1.0175242034032221</v>
       </c>
-      <c r="W15" s="0">
+      <c r="AA15" s="0">
         <v>0.30990379861286077</v>
       </c>
-      <c r="X15" s="0">
+      <c r="AB15" s="0">
+        <v>0.79947318459245309</v>
+      </c>
+      <c r="AC15" s="0">
+        <v>0.42420844449965522</v>
+      </c>
+      <c r="AD15" s="0">
         <v>1.0221843287300141</v>
       </c>
-      <c r="Y15" s="0">
+      <c r="AE15" s="0">
         <v>0.30689401217211021</v>
       </c>
     </row>
@@ -24583,66 +25247,84 @@
         <v>0.80676612796245195</v>
       </c>
       <c r="E16" s="0">
+        <v>0.98496019202325147</v>
+      </c>
+      <c r="F16" s="0">
         <v>0.8205320807279165</v>
       </c>
-      <c r="F16" s="0">
+      <c r="G16" s="0">
         <v>1.2865524951821619</v>
       </c>
-      <c r="G16" s="0">
+      <c r="H16" s="0">
         <v>2.0916981278460987</v>
       </c>
-      <c r="H16" s="0">
+      <c r="I16" s="0">
         <v>0.84444433516521233</v>
       </c>
-      <c r="I16" s="0">
+      <c r="J16" s="0">
+        <v>1.7853992338664515</v>
+      </c>
+      <c r="K16" s="0">
         <v>1.0995469903795632</v>
       </c>
-      <c r="J16" s="0">
+      <c r="L16" s="0">
         <v>0.12219642624378234</v>
       </c>
-      <c r="K16" s="0">
+      <c r="M16" s="0">
         <v>0.90285156628267815</v>
       </c>
-      <c r="L16" s="0">
+      <c r="N16" s="0">
         <v>-7.5723922625978481</v>
       </c>
-      <c r="M16" s="0">
+      <c r="O16" s="0">
         <v>1.0655664370779483e-13</v>
       </c>
-      <c r="N16" s="0">
+      <c r="P16" s="0">
         <v>2.9042358685519187</v>
       </c>
-      <c r="O16" s="0">
+      <c r="Q16" s="0">
         <v>0.004016326570777805</v>
       </c>
-      <c r="P16" s="0">
+      <c r="R16" s="0">
+        <v>-4.986997774861555</v>
+      </c>
+      <c r="S16" s="0">
+        <v>7.242274221402471e-07</v>
+      </c>
+      <c r="T16" s="0">
         <v>2.8114318264846982</v>
       </c>
-      <c r="Q16" s="0">
+      <c r="U16" s="0">
         <v>0.005010202832482125</v>
       </c>
-      <c r="R16" s="0">
+      <c r="V16" s="0">
         <v>-3.5940857554625465</v>
       </c>
-      <c r="S16" s="0">
+      <c r="W16" s="0">
         <v>0.00039923342228134127</v>
       </c>
-      <c r="T16" s="0">
+      <c r="X16" s="0">
         <v>-21.745620722260124</v>
       </c>
-      <c r="U16" s="0">
+      <c r="Y16" s="0">
         <v>7.0923139058125189e-82</v>
       </c>
-      <c r="V16" s="0">
+      <c r="Z16" s="0">
         <v>2.5372652505685651</v>
       </c>
-      <c r="W16" s="0">
+      <c r="AA16" s="0">
         <v>0.011790888975712663</v>
       </c>
-      <c r="X16" s="0">
+      <c r="AB16" s="0">
+        <v>-17.970170536751137</v>
+      </c>
+      <c r="AC16" s="0">
+        <v>1.1002215442231855e-62</v>
+      </c>
+      <c r="AD16" s="0">
         <v>2.3214001469491832</v>
       </c>
-      <c r="Y16" s="0">
+      <c r="AE16" s="0">
         <v>0.020427474957168911</v>
       </c>
     </row>
@@ -24660,66 +25342,84 @@
         <v>0.86027749690000088</v>
       </c>
       <c r="E17" s="0">
+        <v>1.0641485564539563</v>
+      </c>
+      <c r="F17" s="0">
         <v>0.87960959692205687</v>
       </c>
-      <c r="F17" s="0">
+      <c r="G17" s="0">
         <v>1.2914030295432415</v>
       </c>
-      <c r="G17" s="0">
+      <c r="H17" s="0">
         <v>2.0233779159752032</v>
       </c>
-      <c r="H17" s="0">
+      <c r="I17" s="0">
         <v>0.85496962130494381</v>
       </c>
-      <c r="I17" s="0">
+      <c r="J17" s="0">
+        <v>1.7449151273326315</v>
+      </c>
+      <c r="K17" s="0">
         <v>1.0962430998713437</v>
       </c>
-      <c r="J17" s="0">
+      <c r="L17" s="0">
         <v>-1.9821561174813707</v>
       </c>
-      <c r="K17" s="0">
+      <c r="M17" s="0">
         <v>0.048667920089406187</v>
       </c>
-      <c r="L17" s="0">
+      <c r="N17" s="0">
         <v>-11.928266179804075</v>
       </c>
-      <c r="M17" s="0">
+      <c r="O17" s="0">
         <v>3.4783665276903049e-30</v>
       </c>
-      <c r="N17" s="0">
+      <c r="P17" s="0">
         <v>0.29241319950139366</v>
       </c>
-      <c r="O17" s="0">
+      <c r="Q17" s="0">
         <v>0.77021719064478145</v>
       </c>
-      <c r="P17" s="0">
+      <c r="R17" s="0">
+        <v>-10.677177465544764</v>
+      </c>
+      <c r="S17" s="0">
+        <v>2.9271664651700165e-25</v>
+      </c>
+      <c r="T17" s="0">
         <v>0.19947132898909667</v>
       </c>
-      <c r="Q17" s="0">
+      <c r="U17" s="0">
         <v>0.84192693168185428</v>
       </c>
-      <c r="R17" s="0">
+      <c r="V17" s="0">
         <v>-4.0154091974950736</v>
       </c>
-      <c r="S17" s="0">
+      <c r="W17" s="0">
         <v>8.0668177999379078e-05</v>
       </c>
-      <c r="T17" s="0">
+      <c r="X17" s="0">
         <v>-15.623677248103936</v>
       </c>
-      <c r="U17" s="0">
+      <c r="Y17" s="0">
         <v>6.434919141655925e-48</v>
       </c>
-      <c r="V17" s="0">
+      <c r="Z17" s="0">
         <v>0.13518213786993466</v>
       </c>
-      <c r="W17" s="0">
+      <c r="AA17" s="0">
         <v>0.89257841362137391</v>
       </c>
-      <c r="X17" s="0">
+      <c r="AB17" s="0">
+        <v>-14.993233485191466</v>
+      </c>
+      <c r="AC17" s="0">
+        <v>6.1865367967826625e-46</v>
+      </c>
+      <c r="AD17" s="0">
         <v>0.024824183635435641</v>
       </c>
-      <c r="Y17" s="0">
+      <c r="AE17" s="0">
         <v>0.9801992148069697</v>
       </c>
     </row>
@@ -24737,66 +25437,84 @@
         <v>0.93375508903409055</v>
       </c>
       <c r="E18" s="0">
+        <v>1.0844125121785422</v>
+      </c>
+      <c r="F18" s="0">
         <v>0.93500110803849845</v>
       </c>
-      <c r="F18" s="0">
+      <c r="G18" s="0">
         <v>1.2452964112790794</v>
       </c>
-      <c r="G18" s="0">
+      <c r="H18" s="0">
         <v>1.2316252966505936</v>
       </c>
-      <c r="H18" s="0">
+      <c r="I18" s="0">
         <v>0.88810354413982373</v>
       </c>
-      <c r="I18" s="0">
+      <c r="J18" s="0">
+        <v>1.2368261536388128</v>
+      </c>
+      <c r="K18" s="0">
         <v>0.98264586889870109</v>
       </c>
-      <c r="J18" s="0">
+      <c r="L18" s="0">
         <v>-4.4365130371951542</v>
       </c>
-      <c r="K18" s="0">
+      <c r="M18" s="0">
         <v>1.4257141251894093e-05</v>
       </c>
-      <c r="L18" s="0">
+      <c r="N18" s="0">
         <v>-9.3756469251008383</v>
       </c>
-      <c r="M18" s="0">
+      <c r="O18" s="0">
         <v>7.7218167921494704e-20</v>
       </c>
-      <c r="N18" s="0">
+      <c r="P18" s="0">
         <v>1.7365453011034138</v>
       </c>
-      <c r="O18" s="0">
+      <c r="Q18" s="0">
         <v>0.083719330081215584</v>
       </c>
-      <c r="P18" s="0">
+      <c r="R18" s="0">
+        <v>-8.247972480290203</v>
+      </c>
+      <c r="S18" s="0">
+        <v>5.108905100495247e-16</v>
+      </c>
+      <c r="T18" s="0">
         <v>1.6274589069975283</v>
       </c>
-      <c r="Q18" s="0">
+      <c r="U18" s="0">
         <v>0.10389495361496393</v>
       </c>
-      <c r="R18" s="0">
+      <c r="V18" s="0">
         <v>-5.2406986478138977</v>
       </c>
-      <c r="S18" s="0">
+      <c r="W18" s="0">
         <v>3.6523013707611064e-07</v>
       </c>
-      <c r="T18" s="0">
+      <c r="X18" s="0">
         <v>-10.667564511145864</v>
       </c>
-      <c r="U18" s="0">
+      <c r="Y18" s="0">
         <v>7.508118677089376e-25</v>
       </c>
-      <c r="V18" s="0">
+      <c r="Z18" s="0">
         <v>1.3440574583630303</v>
       </c>
-      <c r="W18" s="0">
+      <c r="AA18" s="0">
         <v>0.18016803561227868</v>
       </c>
-      <c r="X18" s="0">
+      <c r="AB18" s="0">
+        <v>-9.0916360006308707</v>
+      </c>
+      <c r="AC18" s="0">
+        <v>5.2326757628495238e-19</v>
+      </c>
+      <c r="AD18" s="0">
         <v>1.2468018517455182</v>
       </c>
-      <c r="Y18" s="0">
+      <c r="AE18" s="0">
         <v>0.21270676308260472</v>
       </c>
     </row>
@@ -24814,66 +25532,84 @@
         <v>1.1292275298338887</v>
       </c>
       <c r="E19" s="0">
+        <v>0.93144689195819064</v>
+      </c>
+      <c r="F19" s="0">
         <v>1.1244400960899368</v>
       </c>
-      <c r="F19" s="0">
+      <c r="G19" s="0">
         <v>0.88660294303262865</v>
       </c>
-      <c r="G19" s="0">
+      <c r="H19" s="0">
         <v>0.74740861968346473</v>
       </c>
-      <c r="H19" s="0">
+      <c r="I19" s="0">
         <v>1.0219026952577144</v>
       </c>
-      <c r="I19" s="0">
+      <c r="J19" s="0">
+        <v>0.80036185641534729</v>
+      </c>
+      <c r="K19" s="0">
         <v>0.96184067070679391</v>
       </c>
-      <c r="J19" s="0">
+      <c r="L19" s="0">
         <v>1.400658802997125</v>
       </c>
-      <c r="K19" s="0">
+      <c r="M19" s="0">
         <v>0.16268158595626114</v>
       </c>
-      <c r="L19" s="0">
+      <c r="N19" s="0">
         <v>2.8355909943611532</v>
       </c>
-      <c r="M19" s="0">
+      <c r="O19" s="0">
         <v>0.0046957956290265114</v>
       </c>
-      <c r="N19" s="0">
+      <c r="P19" s="0">
         <v>-1.6577612802839166</v>
       </c>
-      <c r="O19" s="0">
+      <c r="Q19" s="0">
         <v>0.098640280837824834</v>
       </c>
-      <c r="P19" s="0">
+      <c r="R19" s="0">
+        <v>2.7414173019283399</v>
+      </c>
+      <c r="S19" s="0">
+        <v>0.0062280354601378218</v>
+      </c>
+      <c r="T19" s="0">
         <v>-1.6372719831334313</v>
       </c>
-      <c r="Q19" s="0">
+      <c r="U19" s="0">
         <v>0.10182861567634272</v>
       </c>
-      <c r="R19" s="0">
+      <c r="V19" s="0">
         <v>0.6820729398518649</v>
       </c>
-      <c r="S19" s="0">
+      <c r="W19" s="0">
         <v>0.49588819110550575</v>
       </c>
-      <c r="T19" s="0">
+      <c r="X19" s="0">
         <v>2.2844227994789628</v>
       </c>
-      <c r="U19" s="0">
+      <c r="Y19" s="0">
         <v>0.022621923414648196</v>
       </c>
-      <c r="V19" s="0">
+      <c r="Z19" s="0">
         <v>-1.7488488653954279</v>
       </c>
-      <c r="W19" s="0">
+      <c r="AA19" s="0">
         <v>0.081564397426930724</v>
       </c>
-      <c r="X19" s="0">
+      <c r="AB19" s="0">
+        <v>1.7546030608241128</v>
+      </c>
+      <c r="AC19" s="0">
+        <v>0.079637506394009294</v>
+      </c>
+      <c r="AD19" s="0">
         <v>-1.7368292777132044</v>
       </c>
-      <c r="Y19" s="0">
+      <c r="AE19" s="0">
         <v>0.082666848785762484</v>
       </c>
     </row>
@@ -24891,66 +25627,84 @@
         <v>1.0872209130754165</v>
       </c>
       <c r="E20" s="0">
+        <v>0.97255191391909634</v>
+      </c>
+      <c r="F20" s="0">
         <v>1.0862583217702546</v>
       </c>
-      <c r="F20" s="0">
+      <c r="G20" s="0">
         <v>0.92045356385212584</v>
       </c>
-      <c r="G20" s="0">
+      <c r="H20" s="0">
         <v>1.0691044581226163</v>
       </c>
-      <c r="H20" s="0">
+      <c r="I20" s="0">
         <v>1.1308021416136003</v>
       </c>
-      <c r="I20" s="0">
+      <c r="J20" s="0">
+        <v>1.0125536893461791</v>
+      </c>
+      <c r="K20" s="0">
         <v>1.0987437568918212</v>
       </c>
-      <c r="J20" s="0">
+      <c r="L20" s="0">
         <v>2.0009204536525225</v>
       </c>
-      <c r="K20" s="0">
+      <c r="M20" s="0">
         <v>0.046591883432105345</v>
       </c>
-      <c r="L20" s="0">
+      <c r="N20" s="0">
         <v>0.58829602395445491</v>
       </c>
-      <c r="M20" s="0">
+      <c r="O20" s="0">
         <v>0.55650862257163713</v>
       </c>
-      <c r="N20" s="0">
+      <c r="P20" s="0">
         <v>-1.9051520085235021</v>
       </c>
-      <c r="O20" s="0">
+      <c r="Q20" s="0">
         <v>0.057926395563460638</v>
       </c>
-      <c r="P20" s="0">
+      <c r="R20" s="0">
+        <v>2.0474188340651516</v>
+      </c>
+      <c r="S20" s="0">
+        <v>0.040881276553859147</v>
+      </c>
+      <c r="T20" s="0">
         <v>-1.8902910821175505</v>
       </c>
-      <c r="Q20" s="0">
+      <c r="U20" s="0">
         <v>0.058953187643929837</v>
       </c>
-      <c r="R20" s="0">
+      <c r="V20" s="0">
         <v>2.1573963059240318</v>
       </c>
-      <c r="S20" s="0">
+      <c r="W20" s="0">
         <v>0.032024864644031856</v>
       </c>
-      <c r="T20" s="0">
+      <c r="X20" s="0">
         <v>-5.6668306612415931</v>
       </c>
-      <c r="U20" s="0">
+      <c r="Y20" s="0">
         <v>2.0659545307480813e-08</v>
       </c>
-      <c r="V20" s="0">
+      <c r="Z20" s="0">
         <v>-2.2189790125853488</v>
       </c>
-      <c r="W20" s="0">
+      <c r="AA20" s="0">
         <v>0.027401148835163355</v>
       </c>
-      <c r="X20" s="0">
+      <c r="AB20" s="0">
+        <v>-0.43489248291209315</v>
+      </c>
+      <c r="AC20" s="0">
+        <v>0.66373554059419959</v>
+      </c>
+      <c r="AD20" s="0">
         <v>-2.2100063434716524</v>
       </c>
-      <c r="Y20" s="0">
+      <c r="AE20" s="0">
         <v>0.027287722079434324</v>
       </c>
     </row>
@@ -24968,22 +25722,26 @@
         <v>7.6076125470776352</v>
       </c>
       <c r="E21" s="0">
-        <v>3.3385455969480109</v>
+        <v>0.53180860018070153</v>
       </c>
       <c r="F21" s="0">
+        <v>0.53180860018070153</v>
+      </c>
+      <c r="G21" s="0">
         <v>0.5875749160933138</v>
       </c>
-      <c r="G21" s="0">
+      <c r="H21" s="0">
         <v>0.28708216358625271</v>
       </c>
-      <c r="H21" s="0">
+      <c r="I21" s="0">
         <v>3.8330610688643376</v>
       </c>
-      <c r="I21" s="0">
+      <c r="J21" s="0">
+        <v>0.35642664493403592</v>
+      </c>
+      <c r="K21" s="0">
         <v>1.0517535297200964</v>
       </c>
-      <c r="J21" s="0"/>
-      <c r="K21" s="0"/>
       <c r="L21" s="0"/>
       <c r="M21" s="0"/>
       <c r="N21" s="0"/>
@@ -24998,6 +25756,12 @@
       <c r="W21" s="0"/>
       <c r="X21" s="0"/>
       <c r="Y21" s="0"/>
+      <c r="Z21" s="0"/>
+      <c r="AA21" s="0"/>
+      <c r="AB21" s="0"/>
+      <c r="AC21" s="0"/>
+      <c r="AD21" s="0"/>
+      <c r="AE21" s="0"/>
     </row>
   </sheetData>
 </worksheet>
@@ -25035,61 +25799,61 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="I1" s="0" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="J1" s="0" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="K1" s="0" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="L1" s="0" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="M1" s="0" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="N1" s="0" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="O1" s="0" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="P1" s="0" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="Q1" s="0" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="R1" s="0" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="S1" s="0" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="T1" s="0" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
     </row>
     <row r="2">
@@ -26268,61 +27032,61 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="I1" s="0" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="J1" s="0" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="K1" s="0" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="L1" s="0" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="M1" s="0" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="N1" s="0" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="O1" s="0" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="P1" s="0" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="Q1" s="0" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="R1" s="0" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="S1" s="0" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="T1" s="0" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
     </row>
     <row r="2">
@@ -27501,61 +28265,61 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="I1" s="0" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="J1" s="0" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="K1" s="0" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="L1" s="0" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="M1" s="0" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="N1" s="0" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="O1" s="0" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="P1" s="0" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="Q1" s="0" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="R1" s="0" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="S1" s="0" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="T1" s="0" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
     </row>
     <row r="2">
@@ -28772,61 +29536,61 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="I1" s="0" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="J1" s="0" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="K1" s="0" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="L1" s="0" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="M1" s="0" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="N1" s="0" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="O1" s="0" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="P1" s="0" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="Q1" s="0" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="R1" s="0" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="S1" s="0" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="T1" s="0" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
     </row>
     <row r="2">
@@ -30005,61 +30769,61 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="I1" s="0" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="J1" s="0" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="K1" s="0" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="L1" s="0" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="M1" s="0" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="N1" s="0" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="O1" s="0" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="P1" s="0" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="Q1" s="0" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="R1" s="0" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="S1" s="0" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="T1" s="0" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
     </row>
     <row r="2">
@@ -31238,61 +32002,61 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="I1" s="0" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="J1" s="0" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="K1" s="0" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="L1" s="0" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="M1" s="0" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="N1" s="0" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="O1" s="0" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="P1" s="0" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="Q1" s="0" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="R1" s="0" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="S1" s="0" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="T1" s="0" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
     </row>
     <row r="2">
@@ -32509,61 +33273,61 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="I1" s="0" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="J1" s="0" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="K1" s="0" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="L1" s="0" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="M1" s="0" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="N1" s="0" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="O1" s="0" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="P1" s="0" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="Q1" s="0" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="R1" s="0" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="S1" s="0" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="T1" s="0" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
     </row>
     <row r="2">
@@ -33742,61 +34506,61 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="I1" s="0" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="J1" s="0" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="K1" s="0" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="L1" s="0" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="M1" s="0" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="N1" s="0" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="O1" s="0" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="P1" s="0" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="Q1" s="0" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="R1" s="0" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="S1" s="0" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="T1" s="0" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
     </row>
     <row r="2">
@@ -34975,61 +35739,61 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="I1" s="0" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="J1" s="0" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="K1" s="0" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="L1" s="0" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="M1" s="0" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="N1" s="0" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="O1" s="0" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="P1" s="0" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="Q1" s="0" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="R1" s="0" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="S1" s="0" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="T1" s="0" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
     </row>
     <row r="2">
@@ -36246,25 +37010,25 @@
         <v>23</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I1" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J1" s="0" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="K1" s="0" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2">
